--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
@@ -565,67 +565,67 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1804</v>
+        <v>11.1456</v>
       </c>
       <c r="E2" t="n">
-        <v>12.4614</v>
+        <v>11.1597</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.281</v>
+        <v>-0.0138000000000007</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8613000000000001</v>
+        <v>0.9828000000000003</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8089</v>
+        <v>2.9856</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.947600000000001</v>
+        <v>-2.003399999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>18.2217</v>
+        <v>17.7888</v>
       </c>
       <c r="K2" t="n">
-        <v>7.5078</v>
+        <v>7.288499999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>10.7139</v>
+        <v>10.5006</v>
       </c>
       <c r="M2" t="n">
-        <v>-17.361</v>
+        <v>-16.8063</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.6992</v>
+        <v>-4.3023</v>
       </c>
       <c r="O2" t="n">
-        <v>-12.6618</v>
+        <v>-12.5037</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3845</v>
+        <v>1.3989</v>
       </c>
       <c r="Q2" t="n">
-        <v>-19.3836</v>
+        <v>-19.5861</v>
       </c>
       <c r="R2" t="n">
-        <v>20.7678</v>
+        <v>20.985</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6702000000000004</v>
+        <v>-0.7598999999999996</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.4092</v>
+        <v>-3.8766</v>
       </c>
       <c r="U2" t="n">
-        <v>2.739</v>
+        <v>3.117</v>
       </c>
       <c r="V2" t="n">
-        <v>9.6051</v>
+        <v>9.5235</v>
       </c>
       <c r="W2" t="n">
-        <v>17.0322</v>
+        <v>16.8336</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.4268</v>
+        <v>-7.309799999999999</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>10.4139</v>
+        <v>10.1505</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2336</v>
+        <v>6.392999999999998</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1806</v>
+        <v>3.7575</v>
       </c>
       <c r="G3" t="n">
-        <v>10.5489</v>
+        <v>10.3407</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7947000000000001</v>
+        <v>-0.8283</v>
       </c>
       <c r="I3" t="n">
-        <v>11.3436</v>
+        <v>11.169</v>
       </c>
       <c r="J3" t="n">
-        <v>15.654</v>
+        <v>15.1515</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.9614999999999998</v>
       </c>
       <c r="L3" t="n">
-        <v>16.3635</v>
+        <v>16.113</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.1051</v>
+        <v>-4.8108</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.08550000000000008</v>
+        <v>0.1329</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.0199</v>
+        <v>-4.943700000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0769</v>
+        <v>2.0985</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.1535</v>
+        <v>-4.197</v>
       </c>
       <c r="R3" t="n">
-        <v>6.230399999999999</v>
+        <v>6.295500000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7091</v>
+        <v>-1.749</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.5289</v>
+        <v>-3.7842</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8201</v>
+        <v>2.0349</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5028</v>
+        <v>-0.5394</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7383000000000001</v>
+        <v>-0.7773</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2355</v>
+        <v>0.2379</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3326999999999999</v>
+        <v>0.5262000000000004</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05579999999999985</v>
+        <v>3.131099999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3885</v>
+        <v>-2.6049</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.8228</v>
+        <v>-3.989099999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7066</v>
+        <v>2.9721</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.5294</v>
+        <v>-6.9612</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9401</v>
+        <v>6.6981</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2488</v>
+        <v>6.333299999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3084</v>
+        <v>0.3645000000000003</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.7629</v>
+        <v>-10.6869</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4578</v>
+        <v>-3.361499999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.2207</v>
+        <v>-7.3257</v>
       </c>
       <c r="P4" t="n">
-        <v>6.9228</v>
+        <v>10.4925</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.6924</v>
+        <v>-3.4974</v>
       </c>
       <c r="R4" t="n">
-        <v>7.6149</v>
+        <v>13.9902</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0203</v>
+        <v>-0.3507</v>
       </c>
       <c r="T4" t="n">
-        <v>1.05</v>
+        <v>-3.2712</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0294</v>
+        <v>2.9205</v>
       </c>
       <c r="V4" t="n">
-        <v>-5.7879</v>
+        <v>-5.6268</v>
       </c>
       <c r="W4" t="n">
-        <v>-2.3538</v>
+        <v>3.2019</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.4341</v>
+        <v>-8.8287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2187000000000011</v>
+        <v>0.4863000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7668</v>
+        <v>-0.3228000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.5481</v>
+        <v>0.8094000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.138800000000002</v>
+        <v>-1.7346</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8173</v>
+        <v>2.7576</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.956399999999999</v>
+        <v>-4.4922</v>
       </c>
       <c r="J5" t="n">
-        <v>6.938400000000001</v>
+        <v>1.8546</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4629</v>
+        <v>2.1792</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4752</v>
+        <v>-0.3246000000000002</v>
       </c>
       <c r="M5" t="n">
-        <v>-11.0769</v>
+        <v>-3.5892</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.6453</v>
+        <v>0.5784</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.4316</v>
+        <v>-4.1676</v>
       </c>
       <c r="P5" t="n">
-        <v>10.3839</v>
+        <v>6.9951</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4614</v>
+        <v>-0.6996</v>
       </c>
       <c r="R5" t="n">
-        <v>13.8453</v>
+        <v>7.6947</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3027</v>
+        <v>0.9801000000000002</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.9409</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6382</v>
+        <v>0.08040000000000003</v>
       </c>
       <c r="V5" t="n">
-        <v>-5.7237</v>
+        <v>-5.7543</v>
       </c>
       <c r="W5" t="n">
-        <v>3.231</v>
+        <v>-2.3784</v>
       </c>
       <c r="X5" t="n">
-        <v>-8.954699999999999</v>
+        <v>-3.3759</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09390000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3204</v>
+        <v>-0.3489</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4143</v>
+        <v>0.4488</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0599</v>
+        <v>-1.0458</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4569</v>
+        <v>-0.4503</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.603</v>
+        <v>-0.5955</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0507</v>
+        <v>0.0501</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0507</v>
+        <v>0.0501</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1106</v>
+        <v>-1.0959</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5075999999999999</v>
+        <v>-0.5004</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.603</v>
+        <v>-0.5955</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3845</v>
+        <v>1.3989</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3845</v>
+        <v>1.3989</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2307</v>
+        <v>-0.2532</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3714</v>
+        <v>-0.399</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1407</v>
+        <v>0.1458</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,73 +955,73 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.9421</v>
+        <v>-5.964900000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>8.5212</v>
+        <v>7.6713</v>
       </c>
       <c r="F7" t="n">
-        <v>-14.4633</v>
+        <v>-13.6356</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3772</v>
+        <v>2.263500000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>11.4957</v>
+        <v>11.2794</v>
       </c>
       <c r="I7" t="n">
-        <v>-9.118500000000001</v>
+        <v>-9.0159</v>
       </c>
       <c r="J7" t="n">
-        <v>13.5258</v>
+        <v>13.0818</v>
       </c>
       <c r="K7" t="n">
-        <v>12.0855</v>
+        <v>11.6511</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4403</v>
+        <v>1.4304</v>
       </c>
       <c r="M7" t="n">
-        <v>-11.1486</v>
+        <v>-10.8183</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5901</v>
+        <v>-0.372</v>
       </c>
       <c r="O7" t="n">
-        <v>-10.5588</v>
+        <v>-10.4466</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3845</v>
+        <v>-1.3989</v>
       </c>
       <c r="Q7" t="n">
-        <v>-10.3842</v>
+        <v>-10.4922</v>
       </c>
       <c r="R7" t="n">
-        <v>8.999700000000001</v>
+        <v>9.093299999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1427</v>
+        <v>1.176</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5207</v>
+        <v>-1.7337</v>
       </c>
       <c r="U7" t="n">
-        <v>2.6637</v>
+        <v>2.9097</v>
       </c>
       <c r="V7" t="n">
-        <v>-8.077500000000001</v>
+        <v>-8.004899999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>6.9006</v>
+        <v>6.8157</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.9781</v>
+        <v>-14.8206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>-11.3397</v>
+        <v>-11.328</v>
       </c>
       <c r="E8" t="n">
-        <v>-9.6813</v>
+        <v>-4.068</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6584</v>
+        <v>-7.26</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.2529</v>
+        <v>-7.9035</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.5454</v>
+        <v>-1.0044</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.7075</v>
+        <v>-6.8991</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.4132</v>
+        <v>0.8348999999999996</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.5239</v>
+        <v>2.8797</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1107</v>
+        <v>-2.0454</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.8397</v>
+        <v>-8.7384</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0215</v>
+        <v>-3.885</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.8182</v>
+        <v>-4.8534</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.9994</v>
+        <v>4.197</v>
       </c>
       <c r="Q8" t="n">
-        <v>-10.3839</v>
+        <v>-5.595899999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3848</v>
+        <v>9.792899999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6816000000000001</v>
+        <v>-1.5468</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1152</v>
+        <v>-2.9205</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7968</v>
+        <v>1.3734</v>
       </c>
       <c r="V8" t="n">
-        <v>3.231</v>
+        <v>-6.0747</v>
       </c>
       <c r="W8" t="n">
-        <v>3.231</v>
+        <v>3.613799999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-9.688499999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-11.4102</v>
+        <v>-11.4252</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4611</v>
+        <v>-9.8622</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.9491</v>
+        <v>-1.563</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.0145</v>
+        <v>-6.2037</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1787</v>
+        <v>-3.5172</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.835800000000001</v>
+        <v>-2.6862</v>
       </c>
       <c r="J9" t="n">
-        <v>1.045499999999999</v>
+        <v>-2.4153</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9595</v>
+        <v>-2.5254</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.914</v>
+        <v>0.1101</v>
       </c>
       <c r="M9" t="n">
-        <v>-9.060300000000002</v>
+        <v>-3.7884</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.1382</v>
+        <v>-0.9918</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.9218</v>
+        <v>-2.7963</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1535</v>
+        <v>-9.0936</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.5383</v>
+        <v>-10.4925</v>
       </c>
       <c r="R9" t="n">
-        <v>9.691800000000001</v>
+        <v>1.3992</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4382</v>
+        <v>0.6698999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.6385</v>
+        <v>-0.1562999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>0.8262</v>
       </c>
       <c r="V9" t="n">
-        <v>-6.1113</v>
+        <v>3.2019</v>
       </c>
       <c r="W9" t="n">
-        <v>3.6696</v>
+        <v>3.2019</v>
       </c>
       <c r="X9" t="n">
-        <v>-9.7806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-16.2027</v>
+        <v>-16.2222</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.353899999999999</v>
+        <v>-8.1495</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.8491</v>
+        <v>-8.073</v>
       </c>
       <c r="G10" t="n">
-        <v>-21.0525</v>
+        <v>-21.0306</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.0303</v>
+        <v>-5.974200000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-15.0219</v>
+        <v>-15.0564</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.783999999999999</v>
+        <v>-9.130200000000002</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3997</v>
+        <v>-2.5902</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.3843</v>
+        <v>-6.539999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-12.2679</v>
+        <v>-11.9007</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.6309</v>
+        <v>-3.3843</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.637600000000001</v>
+        <v>-8.5161</v>
       </c>
       <c r="P10" t="n">
-        <v>6.230399999999999</v>
+        <v>6.295199999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8459</v>
+        <v>-4.8966</v>
       </c>
       <c r="R10" t="n">
-        <v>11.0763</v>
+        <v>11.1918</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.4657</v>
+        <v>-5.5578</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.0322</v>
+        <v>-5.3295</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4335</v>
+        <v>-0.2283</v>
       </c>
       <c r="V10" t="n">
-        <v>4.0848</v>
+        <v>4.071</v>
       </c>
       <c r="W10" t="n">
-        <v>11.3085</v>
+        <v>11.2068</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.2237</v>
+        <v>-7.1358</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-19.5015</v>
+        <v>-19.5816</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1534</v>
+        <v>-5.5932</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.3481</v>
+        <v>-13.9884</v>
       </c>
       <c r="G11" t="n">
-        <v>-11.7846</v>
+        <v>-11.7153</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.8057</v>
+        <v>-4.7823</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.9786</v>
+        <v>-6.933</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.06600000000000006</v>
+        <v>-0.1745999999999998</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.7486</v>
+        <v>-2.8218</v>
       </c>
       <c r="L11" t="n">
-        <v>2.6823</v>
+        <v>2.6469</v>
       </c>
       <c r="M11" t="n">
-        <v>-11.7186</v>
+        <v>-11.5407</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.0574</v>
+        <v>-1.9605</v>
       </c>
       <c r="O11" t="n">
-        <v>-9.6609</v>
+        <v>-9.5802</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.230399999999999</v>
+        <v>-6.2955</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.3839</v>
+        <v>-10.4925</v>
       </c>
       <c r="R11" t="n">
-        <v>4.153799999999999</v>
+        <v>4.197</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9251</v>
+        <v>-1.983</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6041</v>
+        <v>-1.7418</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3213</v>
+        <v>-0.2409</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4386000000000003</v>
+        <v>0.4118999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9006</v>
+        <v>6.8157</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.462</v>
+        <v>-6.4041</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.8027</v>
+        <v>-19.6239</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.8904</v>
+        <v>-13.5174</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.912599999999999</v>
+        <v>-6.1062</v>
       </c>
       <c r="G12" t="n">
-        <v>-16.0296</v>
+        <v>-15.8472</v>
       </c>
       <c r="H12" t="n">
-        <v>-14.235</v>
+        <v>-14.1144</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7946</v>
+        <v>-1.7328</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.7639</v>
+        <v>-5.9181</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.087</v>
+        <v>-9.219299999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>3.3234</v>
+        <v>3.3012</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.266</v>
+        <v>-9.928799999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.1483</v>
+        <v>-4.895099999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.1177</v>
+        <v>-5.0343</v>
       </c>
       <c r="P12" t="n">
-        <v>5.538</v>
+        <v>5.5962</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.9994</v>
+        <v>-9.093299999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>14.5374</v>
+        <v>14.6895</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.146</v>
+        <v>-1.2855</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3581</v>
+        <v>-1.7079</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2118</v>
+        <v>0.4227</v>
       </c>
       <c r="V12" t="n">
-        <v>-8.165100000000001</v>
+        <v>-8.0871</v>
       </c>
       <c r="W12" t="n">
-        <v>3.231</v>
+        <v>3.2019</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.3961</v>
+        <v>-11.2893</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>-34.9746</v>
+        <v>-34.9224</v>
       </c>
       <c r="E13" t="n">
-        <v>-26.3835</v>
+        <v>-26.7045</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.591100000000001</v>
+        <v>-8.2179</v>
       </c>
       <c r="G13" t="n">
-        <v>-28.959</v>
+        <v>-28.8078</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.7023</v>
+        <v>-6.6063</v>
       </c>
       <c r="I13" t="n">
-        <v>-22.2573</v>
+        <v>-22.2012</v>
       </c>
       <c r="J13" t="n">
-        <v>-16.2225</v>
+        <v>-16.2708</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.6261</v>
+        <v>-3.6495</v>
       </c>
       <c r="L13" t="n">
-        <v>-12.5961</v>
+        <v>-12.6213</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.7368</v>
+        <v>-12.5373</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.0762</v>
+        <v>-2.9571</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.661200000000001</v>
+        <v>-9.5799</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.153500000000001</v>
+        <v>-4.1973</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.3839</v>
+        <v>-10.4925</v>
       </c>
       <c r="R13" t="n">
-        <v>6.230399999999999</v>
+        <v>6.2955</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9306</v>
+        <v>0.873</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2157</v>
+        <v>-0.3527999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1463</v>
+        <v>1.2255</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.7924</v>
+        <v>-2.79</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4386</v>
+        <v>0.4119</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.231</v>
+        <v>-3.2019</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>-46.4073</v>
+        <v>-46.7013</v>
       </c>
       <c r="E14" t="n">
-        <v>-42.435</v>
+        <v>-43.6266</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.9726</v>
+        <v>-3.075299999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-36.0732</v>
+        <v>-36.1392</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.0929</v>
+        <v>-10.1064</v>
       </c>
       <c r="I14" t="n">
-        <v>-25.98</v>
+        <v>-26.0331</v>
       </c>
       <c r="J14" t="n">
-        <v>-19.2558</v>
+        <v>-19.7019</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.4373</v>
+        <v>-4.710599999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-14.8188</v>
+        <v>-14.991</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.8171</v>
+        <v>-16.437</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.6556</v>
+        <v>-5.3955</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.1612</v>
+        <v>-11.0418</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.4611</v>
+        <v>-3.4974</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.1526</v>
+        <v>-22.3839</v>
       </c>
       <c r="R14" t="n">
-        <v>18.6912</v>
+        <v>18.8868</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.8116</v>
+        <v>-5.9673</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.2737</v>
+        <v>-5.6121</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5382</v>
+        <v>-0.3552</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0614</v>
+        <v>-1.0974</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2474</v>
+        <v>4.071899999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.3085</v>
+        <v>-5.1696</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>-143.3412</v>
+        <v>-143.3607</v>
       </c>
       <c r="E15" t="n">
-        <v>-75.7518</v>
+        <v>-83.83799999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-67.58999999999999</v>
+        <v>-59.5224</v>
       </c>
       <c r="G15" t="n">
-        <v>-121.4004</v>
+        <v>-120.8298</v>
       </c>
       <c r="H15" t="n">
-        <v>-28.0134</v>
+        <v>-27.3891</v>
       </c>
       <c r="I15" t="n">
-        <v>-93.38700000000001</v>
+        <v>-93.44099999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>4.870799999999992</v>
+        <v>1.84889999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>5.783400000000002</v>
+        <v>3.903599999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9122999999999983</v>
+        <v>-2.0556</v>
       </c>
       <c r="M15" t="n">
-        <v>-126.2715</v>
+        <v>-122.6787</v>
       </c>
       <c r="N15" t="n">
-        <v>-33.798</v>
+        <v>-31.2942</v>
       </c>
       <c r="O15" t="n">
-        <v>-92.47439999999999</v>
+        <v>-91.3848</v>
       </c>
       <c r="P15" t="n">
-        <v>13.8456</v>
+        <v>13.9896</v>
       </c>
       <c r="Q15" t="n">
-        <v>-110.763</v>
+        <v>-111.9195</v>
       </c>
       <c r="R15" t="n">
-        <v>124.6083</v>
+        <v>125.9103</v>
       </c>
       <c r="S15" t="n">
-        <v>-14.9241</v>
+        <v>-15.7542</v>
       </c>
       <c r="T15" t="n">
-        <v>-26.9586</v>
+        <v>-29.9856</v>
       </c>
       <c r="U15" t="n">
-        <v>12.0342</v>
+        <v>14.2317</v>
       </c>
       <c r="V15" t="n">
-        <v>-20.8626</v>
+        <v>-20.7663</v>
       </c>
       <c r="W15" t="n">
-        <v>57.0984</v>
+        <v>56.2194</v>
       </c>
       <c r="X15" t="n">
-        <v>-77.9601</v>
+        <v>-76.98629999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1456</v>
+        <v>2.2777</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1597</v>
+        <v>4.0944</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0138000000000007</v>
+        <v>-1.8164</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9828000000000003</v>
+        <v>3.159</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9856</v>
+        <v>2.115</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.003399999999999</v>
+        <v>1.0441</v>
       </c>
       <c r="J2" t="n">
-        <v>17.7888</v>
+        <v>5.1208</v>
       </c>
       <c r="K2" t="n">
-        <v>7.288499999999999</v>
+        <v>2.0561</v>
       </c>
       <c r="L2" t="n">
-        <v>10.5006</v>
+        <v>3.0647</v>
       </c>
       <c r="M2" t="n">
-        <v>-16.8063</v>
+        <v>-1.9618</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.3023</v>
+        <v>0.05900000000000002</v>
       </c>
       <c r="O2" t="n">
-        <v>-12.5037</v>
+        <v>-2.0208</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3989</v>
+        <v>1.836</v>
       </c>
       <c r="Q2" t="n">
-        <v>-19.5861</v>
+        <v>-1.1475</v>
       </c>
       <c r="R2" t="n">
-        <v>20.985</v>
+        <v>2.9835</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7598999999999996</v>
+        <v>0.8305</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.8766</v>
+        <v>-0.9609</v>
       </c>
       <c r="U2" t="n">
-        <v>3.117</v>
+        <v>1.7917</v>
       </c>
       <c r="V2" t="n">
-        <v>9.5235</v>
+        <v>-3.5477</v>
       </c>
       <c r="W2" t="n">
-        <v>16.8336</v>
+        <v>1.082</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.309799999999999</v>
+        <v>-4.629799999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>10.1505</v>
+        <v>1.4131</v>
       </c>
       <c r="E3" t="n">
-        <v>6.392999999999998</v>
+        <v>-0.6304000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7575</v>
+        <v>2.0436</v>
       </c>
       <c r="G3" t="n">
-        <v>10.3407</v>
+        <v>-2.2054</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8283</v>
+        <v>0.8803000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>11.169</v>
+        <v>-3.0857</v>
       </c>
       <c r="J3" t="n">
-        <v>15.1515</v>
+        <v>-0.7557</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9614999999999998</v>
+        <v>0.8213</v>
       </c>
       <c r="L3" t="n">
-        <v>16.113</v>
+        <v>-1.577</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.8108</v>
+        <v>-1.4499</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1329</v>
+        <v>0.059</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.943700000000001</v>
+        <v>-1.5089</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0985</v>
+        <v>3.213</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.197</v>
+        <v>-1.6065</v>
       </c>
       <c r="R3" t="n">
-        <v>6.295500000000001</v>
+        <v>4.819500000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.749</v>
+        <v>-0.05219999999999997</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.7842</v>
+        <v>-0.7341</v>
       </c>
       <c r="U3" t="n">
-        <v>2.0349</v>
+        <v>0.6819999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5394</v>
+        <v>0.4577999999999998</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7773</v>
+        <v>2.4658</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2379</v>
+        <v>-2.008</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5262000000000004</v>
+        <v>1.3998</v>
       </c>
       <c r="E4" t="n">
-        <v>3.131099999999999</v>
+        <v>4.7761</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6049</v>
+        <v>-3.3763</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.989099999999999</v>
+        <v>-5.411900000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9721</v>
+        <v>-1.2012</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.9612</v>
+        <v>-4.2107</v>
       </c>
       <c r="J4" t="n">
-        <v>6.6981</v>
+        <v>0.6897000000000002</v>
       </c>
       <c r="K4" t="n">
-        <v>6.333299999999999</v>
+        <v>0.4008</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3645000000000003</v>
+        <v>0.2890000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-10.6869</v>
+        <v>-6.1017</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.361499999999999</v>
+        <v>-1.602</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.3257</v>
+        <v>-4.499700000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>10.4925</v>
+        <v>3.4425</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4974</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>13.9902</v>
+        <v>3.4425</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3507</v>
+        <v>-2.0407</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.2712</v>
+        <v>-2.4058</v>
       </c>
       <c r="U4" t="n">
-        <v>2.9205</v>
+        <v>0.3651</v>
       </c>
       <c r="V4" t="n">
-        <v>-5.6268</v>
+        <v>5.41</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2019</v>
+        <v>6.492</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.8287</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4863000000000001</v>
+        <v>0.3890000000000002</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3228000000000001</v>
+        <v>-2.5998</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8094000000000001</v>
+        <v>2.9888</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7346</v>
+        <v>-5.868600000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7576</v>
+        <v>-1.8296</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.4922</v>
+        <v>-4.039</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8546</v>
+        <v>-1.5251</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1792</v>
+        <v>-1.4065</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3246000000000002</v>
+        <v>-0.1185999999999998</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.5892</v>
+        <v>-4.3435</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5784</v>
+        <v>-0.4230999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.1676</v>
+        <v>-3.9204</v>
       </c>
       <c r="P5" t="n">
-        <v>6.9951</v>
+        <v>0.2295</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.6996</v>
+        <v>-6.1963</v>
       </c>
       <c r="R5" t="n">
-        <v>7.6947</v>
+        <v>6.426</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9801000000000002</v>
+        <v>1.0914</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8999999999999999</v>
+        <v>-0.8918</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08040000000000003</v>
+        <v>1.9833</v>
       </c>
       <c r="V5" t="n">
-        <v>-5.7543</v>
+        <v>4.9367</v>
       </c>
       <c r="W5" t="n">
-        <v>-2.3784</v>
+        <v>6.0136</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.3759</v>
+        <v>-1.0769</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. LOPEZ DE LA TORRE</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1002</v>
+        <v>0.3307000000000002</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3489</v>
+        <v>-1.145</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4488</v>
+        <v>1.4755</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0458</v>
+        <v>0.4664999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4503</v>
+        <v>-1.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5955</v>
+        <v>1.616099999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0501</v>
+        <v>4.2691</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0501</v>
+        <v>-0.4118</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.680899999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0959</v>
+        <v>-3.8025</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5004</v>
+        <v>-0.7376</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5955</v>
+        <v>-3.0648</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3989</v>
+        <v>0.918</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.754</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3989</v>
+        <v>3.672</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2532</v>
+        <v>-0.7315</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.399</v>
+        <v>-2.1815</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1458</v>
+        <v>1.45</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3224</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.4786</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.964900000000002</v>
+        <v>-0.806</v>
       </c>
       <c r="E7" t="n">
-        <v>7.6713</v>
+        <v>-1.1222</v>
       </c>
       <c r="F7" t="n">
-        <v>-13.6356</v>
+        <v>0.3163</v>
       </c>
       <c r="G7" t="n">
-        <v>2.263500000000001</v>
+        <v>-0.3810999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>11.2794</v>
+        <v>0.02300000000000013</v>
       </c>
       <c r="I7" t="n">
-        <v>-9.0159</v>
+        <v>-0.4041</v>
       </c>
       <c r="J7" t="n">
-        <v>13.0818</v>
+        <v>0.5454</v>
       </c>
       <c r="K7" t="n">
-        <v>11.6511</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4304</v>
+        <v>0.5254</v>
       </c>
       <c r="M7" t="n">
-        <v>-10.8183</v>
+        <v>-0.9265</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.372</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="O7" t="n">
-        <v>-10.4466</v>
+        <v>-0.9295</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3989</v>
+        <v>2.5245</v>
       </c>
       <c r="Q7" t="n">
-        <v>-10.4922</v>
+        <v>-0.459</v>
       </c>
       <c r="R7" t="n">
-        <v>9.093299999999999</v>
+        <v>2.9835</v>
       </c>
       <c r="S7" t="n">
-        <v>1.176</v>
+        <v>0.6194</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.7337</v>
+        <v>0.3522</v>
       </c>
       <c r="U7" t="n">
-        <v>2.9097</v>
+        <v>0.2672</v>
       </c>
       <c r="V7" t="n">
-        <v>-8.004899999999999</v>
+        <v>-3.5686</v>
       </c>
       <c r="W7" t="n">
-        <v>6.8157</v>
+        <v>-1.5606</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.8206</v>
+        <v>-2.008</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-11.328</v>
+        <v>-2.804</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.068</v>
+        <v>-1.1222</v>
       </c>
       <c r="F8" t="n">
-        <v>-7.26</v>
+        <v>-1.6817</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.9035</v>
+        <v>-1.9763</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0044</v>
+        <v>-0.5821000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.8991</v>
+        <v>-1.3942</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8348999999999996</v>
+        <v>1.2878</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8797</v>
+        <v>0.1762000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0454</v>
+        <v>1.1116</v>
       </c>
       <c r="M8" t="n">
-        <v>-8.7384</v>
+        <v>-3.2642</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.885</v>
+        <v>-0.7583</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.8534</v>
+        <v>-2.5059</v>
       </c>
       <c r="P8" t="n">
-        <v>4.197</v>
+        <v>1.377</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.595899999999999</v>
+        <v>-3.9015</v>
       </c>
       <c r="R8" t="n">
-        <v>9.792899999999999</v>
+        <v>5.2785</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5468</v>
+        <v>0.8854000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.9205</v>
+        <v>0.4094000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3734</v>
+        <v>0.476</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.0747</v>
+        <v>-3.09</v>
       </c>
       <c r="W8" t="n">
-        <v>3.613799999999999</v>
+        <v>1.082</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.688499999999999</v>
+        <v>-4.172000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1108,67 +1108,67 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-11.4252</v>
+        <v>-5.375</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.8622</v>
+        <v>-5.1324</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.563</v>
+        <v>-0.2426</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.2037</v>
+        <v>-1.1762</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.5172</v>
+        <v>-0.0176</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6862</v>
+        <v>-1.1586</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.4153</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.5254</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1101</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.7884</v>
+        <v>-1.1762</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9918</v>
+        <v>-0.0176</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.7963</v>
+        <v>-1.1586</v>
       </c>
       <c r="P9" t="n">
-        <v>-9.0936</v>
+        <v>-4.131</v>
       </c>
       <c r="Q9" t="n">
-        <v>-10.4925</v>
+        <v>-4.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3992</v>
+        <v>0.459</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6698999999999999</v>
+        <v>-0.0678</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1562999999999999</v>
+        <v>-0.5424</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8262</v>
+        <v>0.4746</v>
       </c>
       <c r="V9" t="n">
-        <v>3.2019</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.2019</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-16.2222</v>
+        <v>-6.879</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.1495</v>
+        <v>-2.0522</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.073</v>
+        <v>-4.8268</v>
       </c>
       <c r="G10" t="n">
-        <v>-21.0306</v>
+        <v>-0.9466</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.974200000000001</v>
+        <v>-1.6204</v>
       </c>
       <c r="I10" t="n">
-        <v>-15.0564</v>
+        <v>0.6738</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.130200000000002</v>
+        <v>1.894</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.5902</v>
+        <v>-1.5146</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.539999999999999</v>
+        <v>3.4086</v>
       </c>
       <c r="M10" t="n">
-        <v>-11.9007</v>
+        <v>-2.8406</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.3843</v>
+        <v>-0.1058</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.5161</v>
+        <v>-2.735</v>
       </c>
       <c r="P10" t="n">
-        <v>6.295199999999999</v>
+        <v>-2.295</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8966</v>
+        <v>-4.59</v>
       </c>
       <c r="R10" t="n">
-        <v>11.1918</v>
+        <v>2.295</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.5578</v>
+        <v>-1.4734</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.3295</v>
+        <v>-1.5204</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2283</v>
+        <v>0.047</v>
       </c>
       <c r="V10" t="n">
-        <v>4.071</v>
+        <v>-2.164</v>
       </c>
       <c r="W10" t="n">
-        <v>11.2068</v>
+        <v>2.164</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.1358</v>
+        <v>-4.328</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-19.5816</v>
+        <v>-7.861599999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5932</v>
+        <v>-3.2731</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.9884</v>
+        <v>-4.588500000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-11.7153</v>
+        <v>-3.2536</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.7823</v>
+        <v>-1.3912</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.933</v>
+        <v>-1.8624</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1745999999999998</v>
+        <v>-0.8068</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.8218</v>
+        <v>-1.2884</v>
       </c>
       <c r="L11" t="n">
-        <v>2.6469</v>
+        <v>0.4818</v>
       </c>
       <c r="M11" t="n">
-        <v>-11.5407</v>
+        <v>-2.4468</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9605</v>
+        <v>-0.1027</v>
       </c>
       <c r="O11" t="n">
-        <v>-9.5802</v>
+        <v>-2.3442</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.2955</v>
+        <v>-0.918</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.4925</v>
+        <v>-3.4425</v>
       </c>
       <c r="R11" t="n">
-        <v>4.197</v>
+        <v>2.5245</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.983</v>
+        <v>-0.1422</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.7418</v>
+        <v>-1.188</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2409</v>
+        <v>1.0458</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4118999999999999</v>
+        <v>-3.5478</v>
       </c>
       <c r="W11" t="n">
-        <v>6.8157</v>
+        <v>2.164</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.4041</v>
+        <v>-5.7118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>J. HANDS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.6239</v>
+        <v>-11.7293</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.5174</v>
+        <v>-10.6942</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.1062</v>
+        <v>-1.0351</v>
       </c>
       <c r="G12" t="n">
-        <v>-15.8472</v>
+        <v>-8.423300000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-14.1144</v>
+        <v>-3.0069</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7328</v>
+        <v>-5.416399999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.9181</v>
+        <v>-6.3146</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.219299999999999</v>
+        <v>-2.5688</v>
       </c>
       <c r="L12" t="n">
-        <v>3.3012</v>
+        <v>-3.7457</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.928799999999999</v>
+        <v>-2.1085</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.895099999999999</v>
+        <v>-0.4379999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.0343</v>
+        <v>-1.6704</v>
       </c>
       <c r="P12" t="n">
-        <v>5.5962</v>
+        <v>-2.754</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.093299999999999</v>
+        <v>-4.59</v>
       </c>
       <c r="R12" t="n">
-        <v>14.6895</v>
+        <v>1.836</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2855</v>
+        <v>0.2282</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7079</v>
+        <v>-0.0912</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4227</v>
+        <v>0.3194</v>
       </c>
       <c r="V12" t="n">
-        <v>-8.0871</v>
+        <v>-0.7802</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2019</v>
+        <v>0.3018</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.2893</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. HANDS</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-34.9224</v>
+        <v>-18.2275</v>
       </c>
       <c r="E13" t="n">
-        <v>-26.7045</v>
+        <v>-16.9636</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.2179</v>
+        <v>-1.2639</v>
       </c>
       <c r="G13" t="n">
-        <v>-28.8078</v>
+        <v>-15.9627</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.6063</v>
+        <v>-2.6705</v>
       </c>
       <c r="I13" t="n">
-        <v>-22.2012</v>
+        <v>-13.292</v>
       </c>
       <c r="J13" t="n">
-        <v>-16.2708</v>
+        <v>-11.9487</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.6495</v>
+        <v>-2.3414</v>
       </c>
       <c r="L13" t="n">
-        <v>-12.6213</v>
+        <v>-9.6073</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.5373</v>
+        <v>-4.0139</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.9571</v>
+        <v>-0.3291</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.5799</v>
+        <v>-3.6846</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.1973</v>
+        <v>1.1475</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.4925</v>
+        <v>-3.4425</v>
       </c>
       <c r="R13" t="n">
-        <v>6.2955</v>
+        <v>4.59</v>
       </c>
       <c r="S13" t="n">
-        <v>0.873</v>
+        <v>-0.9467</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3527999999999999</v>
+        <v>-1.094</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2255</v>
+        <v>0.1473</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.79</v>
+        <v>-2.4659</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4119</v>
+        <v>-0.4785</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.2019</v>
+        <v>-1.9873</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,148 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-46.7013</v>
+        <v>-47.8721</v>
       </c>
       <c r="E14" t="n">
-        <v>-43.6266</v>
+        <v>-35.8646</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.075299999999999</v>
+        <v>-12.0071</v>
       </c>
       <c r="G14" t="n">
-        <v>-36.1392</v>
+        <v>-41.9802</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.1064</v>
+        <v>-10.4506</v>
       </c>
       <c r="I14" t="n">
-        <v>-26.0331</v>
+        <v>-31.5291</v>
       </c>
       <c r="J14" t="n">
-        <v>-19.7019</v>
+        <v>-7.5441</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.710599999999999</v>
+        <v>-6.0571</v>
       </c>
       <c r="L14" t="n">
-        <v>-14.991</v>
+        <v>-1.486600000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.437</v>
+        <v>-34.4361</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.3955</v>
+        <v>-4.393199999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.0418</v>
+        <v>-30.0428</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.4974</v>
+        <v>4.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.3839</v>
+        <v>-36.7198</v>
       </c>
       <c r="R14" t="n">
-        <v>18.8868</v>
+        <v>41.31</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.9673</v>
+        <v>-1.7996</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.6121</v>
+        <v>-10.8485</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3552</v>
+        <v>9.049399999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0974</v>
+        <v>-8.6821</v>
       </c>
       <c r="W14" t="n">
-        <v>4.071899999999999</v>
+        <v>19.24750000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.1696</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>UCAM Murcia</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-143.3607</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-83.83799999999999</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-59.5224</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-120.8298</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-27.3891</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-93.44099999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.84889999999999</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.903599999999999</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-2.0556</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-122.6787</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-31.2942</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-91.3848</v>
-      </c>
-      <c r="P15" t="n">
-        <v>13.9896</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-111.9195</v>
-      </c>
-      <c r="R15" t="n">
-        <v>125.9103</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-15.7542</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-29.9856</v>
-      </c>
-      <c r="U15" t="n">
-        <v>14.2317</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-20.7663</v>
-      </c>
-      <c r="W15" t="n">
-        <v>56.2194</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-76.98629999999999</v>
+        <v>-27.9298</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
@@ -565,67 +565,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2777</v>
+        <v>2.4541</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0944</v>
+        <v>3.715100000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8164</v>
+        <v>-1.2609</v>
       </c>
       <c r="G2" t="n">
-        <v>3.159</v>
+        <v>3.1924</v>
       </c>
       <c r="H2" t="n">
-        <v>2.115</v>
+        <v>2.17</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0441</v>
+        <v>1.0224</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1208</v>
+        <v>4.9733</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0561</v>
+        <v>1.9815</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0647</v>
+        <v>2.9917</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9618</v>
+        <v>-1.7809</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05900000000000002</v>
+        <v>0.1884</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.0208</v>
+        <v>-1.9693</v>
       </c>
       <c r="P2" t="n">
-        <v>1.836</v>
+        <v>1.8717</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9835</v>
+        <v>3.0416</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8305</v>
+        <v>0.8509</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9609</v>
+        <v>-1.1524</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7917</v>
+        <v>2.0035</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.5477</v>
+        <v>-3.461</v>
       </c>
       <c r="W2" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.629799999999999</v>
+        <v>-4.5251</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4131</v>
+        <v>1.4037</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6304000000000001</v>
+        <v>-1.0614</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0436</v>
+        <v>2.465</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.2054</v>
+        <v>-2.1572</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8803000000000001</v>
+        <v>0.9473</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.0857</v>
+        <v>-3.1044</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7557</v>
+        <v>-0.8711000000000002</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8213</v>
+        <v>0.7587999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.577</v>
+        <v>-1.6299</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4499</v>
+        <v>-1.2861</v>
       </c>
       <c r="N3" t="n">
-        <v>0.059</v>
+        <v>0.1884999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5089</v>
+        <v>-1.4743</v>
       </c>
       <c r="P3" t="n">
-        <v>3.213</v>
+        <v>3.2757</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.6065</v>
+        <v>-1.6379</v>
       </c>
       <c r="R3" t="n">
-        <v>4.819500000000001</v>
+        <v>4.9133</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05219999999999997</v>
+        <v>-0.1424</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7341</v>
+        <v>-0.9491999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.8068000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4577999999999998</v>
+        <v>0.4278</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4658</v>
+        <v>2.3968</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.008</v>
+        <v>-1.969</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3998</v>
+        <v>1.3262</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7761</v>
+        <v>4.2187</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.3763</v>
+        <v>-2.8926</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.411900000000001</v>
+        <v>-5.3994</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2012</v>
+        <v>-1.1819</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.2107</v>
+        <v>-4.2175</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6897000000000002</v>
+        <v>0.4628000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4008</v>
+        <v>0.2675</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2890000000000001</v>
+        <v>0.1953</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.1017</v>
+        <v>-5.862200000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.602</v>
+        <v>-1.4494</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.499700000000001</v>
+        <v>-4.4128</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4425</v>
+        <v>3.5097</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4425</v>
+        <v>3.5097</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.0407</v>
+        <v>-2.1044</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.4058</v>
+        <v>-2.6288</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3651</v>
+        <v>0.5243</v>
       </c>
       <c r="V4" t="n">
-        <v>5.41</v>
+        <v>5.3206</v>
       </c>
       <c r="W4" t="n">
-        <v>6.492</v>
+        <v>6.3847</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3890000000000002</v>
+        <v>0.3487999999999998</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.5998</v>
+        <v>-3.3693</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9888</v>
+        <v>3.7181</v>
       </c>
       <c r="G5" t="n">
-        <v>-5.868600000000001</v>
+        <v>-5.7576</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8296</v>
+        <v>-1.7078</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.039</v>
+        <v>-4.049799999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5251</v>
+        <v>-1.6998</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4065</v>
+        <v>-1.4924</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1185999999999998</v>
+        <v>-0.2073999999999998</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.3435</v>
+        <v>-4.057799999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4230999999999999</v>
+        <v>-0.2156000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.9204</v>
+        <v>-3.8424</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2295</v>
+        <v>0.2338999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.1963</v>
+        <v>-6.3173</v>
       </c>
       <c r="R5" t="n">
-        <v>6.426</v>
+        <v>6.5512</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0914</v>
+        <v>1.0541</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8918</v>
+        <v>-1.21</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9833</v>
+        <v>2.2641</v>
       </c>
       <c r="V5" t="n">
-        <v>4.9367</v>
+        <v>4.8184</v>
       </c>
       <c r="W5" t="n">
-        <v>6.0136</v>
+        <v>5.8578</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0769</v>
+        <v>-1.0392</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3307000000000002</v>
+        <v>0.1707999999999998</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.145</v>
+        <v>-1.8894</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4755</v>
+        <v>2.0602</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4664999999999999</v>
+        <v>0.3755999999999995</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1494</v>
+        <v>-1.1397</v>
       </c>
       <c r="I6" t="n">
-        <v>1.616099999999999</v>
+        <v>1.515499999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2691</v>
+        <v>3.9014</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4118</v>
+        <v>-0.6057999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>4.680899999999999</v>
+        <v>4.507199999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.8025</v>
+        <v>-3.5258</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7376</v>
+        <v>-0.5341</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.0648</v>
+        <v>-2.9917</v>
       </c>
       <c r="P6" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.754</v>
+        <v>-2.8076</v>
       </c>
       <c r="R6" t="n">
-        <v>3.672</v>
+        <v>3.7435</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7315</v>
+        <v>-0.7729999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.1815</v>
+        <v>-2.4562</v>
       </c>
       <c r="U6" t="n">
-        <v>1.45</v>
+        <v>1.6833</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3224</v>
+        <v>-0.3678</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4786</v>
+        <v>-0.5268</v>
       </c>
       <c r="X6" t="n">
-        <v>0.156</v>
+        <v>0.1592</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.806</v>
+        <v>-0.7433000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1222</v>
+        <v>-1.3455</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3163</v>
+        <v>0.6021</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3810999999999999</v>
+        <v>-0.3346999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02300000000000013</v>
+        <v>0.05929999999999991</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4041</v>
+        <v>-0.3938</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5454</v>
+        <v>0.4886</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02000000000000002</v>
+        <v>-0.02159999999999984</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5254</v>
+        <v>0.5099</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9265</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.08079999999999998</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9295</v>
+        <v>-0.9038999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5245</v>
+        <v>2.5738</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.459</v>
+        <v>-0.468</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9835</v>
+        <v>3.0416</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6194</v>
+        <v>0.5777999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3522</v>
+        <v>0.2252</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2672</v>
+        <v>0.3527</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.5686</v>
+        <v>-3.5602</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.5606</v>
+        <v>-1.591</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.008</v>
+        <v>-1.9692</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.804</v>
+        <v>-2.7133</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1222</v>
+        <v>-1.5511</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6817</v>
+        <v>-1.1622</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9763</v>
+        <v>-1.8899</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5821000000000001</v>
+        <v>-0.534</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3942</v>
+        <v>-1.3557</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2878</v>
+        <v>1.1879</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1762000000000001</v>
+        <v>0.08979999999999988</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1116</v>
+        <v>1.0981</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.2642</v>
+        <v>-3.0776</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7583</v>
+        <v>-0.6238</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.5059</v>
+        <v>-2.454</v>
       </c>
       <c r="P8" t="n">
-        <v>1.377</v>
+        <v>1.4039</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9015</v>
+        <v>-3.9775</v>
       </c>
       <c r="R8" t="n">
-        <v>5.2785</v>
+        <v>5.3813</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8854000000000001</v>
+        <v>0.8061</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4094000000000001</v>
+        <v>0.1746000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.476</v>
+        <v>0.6315</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.09</v>
+        <v>-3.0333</v>
       </c>
       <c r="W8" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.172000000000001</v>
+        <v>-4.0974</v>
       </c>
     </row>
     <row r="9">
@@ -1111,22 +1111,22 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.375</v>
+        <v>-5.434</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.1324</v>
+        <v>-5.259</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2426</v>
+        <v>-0.175</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1762</v>
+        <v>-1.15</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0176</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1586</v>
+        <v>-1.141</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1138,31 +1138,31 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1762</v>
+        <v>-1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0176</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1586</v>
+        <v>-1.141</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.131</v>
+        <v>-4.2114</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.59</v>
+        <v>-4.6794</v>
       </c>
       <c r="R9" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0678</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5424</v>
+        <v>-0.5794</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4746</v>
+        <v>0.507</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.879</v>
+        <v>-6.8848</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0522</v>
+        <v>-2.3404</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.8268</v>
+        <v>-4.5444</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9466</v>
+        <v>-0.8932</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6204</v>
+        <v>-1.5696</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6738</v>
+        <v>0.6764</v>
       </c>
       <c r="J10" t="n">
-        <v>1.894</v>
+        <v>1.8516</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5146</v>
+        <v>-1.5158</v>
       </c>
       <c r="L10" t="n">
-        <v>3.4086</v>
+        <v>3.3674</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8406</v>
+        <v>-2.745</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1058</v>
+        <v>-0.0538</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.735</v>
+        <v>-2.691</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.295</v>
+        <v>-2.3398</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.59</v>
+        <v>-4.6794</v>
       </c>
       <c r="R10" t="n">
-        <v>2.295</v>
+        <v>2.3398</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4734</v>
+        <v>-1.5236</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5204</v>
+        <v>-1.641</v>
       </c>
       <c r="U10" t="n">
-        <v>0.047</v>
+        <v>0.1172</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="W10" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.328</v>
+        <v>-4.2564</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.861599999999999</v>
+        <v>-7.815199999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2731</v>
+        <v>-3.741000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.588500000000001</v>
+        <v>-4.074400000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.2536</v>
+        <v>-3.2693</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3912</v>
+        <v>-1.453</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8624</v>
+        <v>-1.8165</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8068</v>
+        <v>-1.004</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2884</v>
+        <v>-1.4798</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4818</v>
+        <v>0.4758</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4468</v>
+        <v>-2.2655</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1027</v>
+        <v>0.02679999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.3442</v>
+        <v>-2.2924</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.918</v>
+        <v>-0.9358</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4425</v>
+        <v>-3.5097</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5245</v>
+        <v>2.5737</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1422</v>
+        <v>-0.1491</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.188</v>
+        <v>-1.3556</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0458</v>
+        <v>1.2066</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.5478</v>
+        <v>-3.461</v>
       </c>
       <c r="W11" t="n">
-        <v>2.164</v>
+        <v>2.1283</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.7118</v>
+        <v>-5.5891</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.7293</v>
+        <v>-11.7671</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.6942</v>
+        <v>-10.9435</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0351</v>
+        <v>-0.8235999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.423300000000001</v>
+        <v>-8.3462</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.0069</v>
+        <v>-2.9648</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.416399999999999</v>
+        <v>-5.381600000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.3146</v>
+        <v>-6.3289</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.5688</v>
+        <v>-2.5832</v>
       </c>
       <c r="L12" t="n">
         <v>-3.7457</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1085</v>
+        <v>-2.0173</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4379999999999999</v>
+        <v>-0.3814</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6704</v>
+        <v>-1.6359</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.754</v>
+        <v>-2.8077</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.59</v>
+        <v>-4.6795</v>
       </c>
       <c r="R12" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2282</v>
+        <v>0.1823</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0912</v>
+        <v>-0.2037</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3194</v>
+        <v>0.386</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7802</v>
+        <v>-0.7955000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3018</v>
+        <v>0.2686</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.2275</v>
+        <v>-18.1911</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.9636</v>
+        <v>-17.3732</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2639</v>
+        <v>-0.8178999999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.9627</v>
+        <v>-15.9444</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.6705</v>
+        <v>-2.6905</v>
       </c>
       <c r="I13" t="n">
-        <v>-13.292</v>
+        <v>-13.254</v>
       </c>
       <c r="J13" t="n">
-        <v>-11.9487</v>
+        <v>-12.0701</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.3414</v>
+        <v>-2.4436</v>
       </c>
       <c r="L13" t="n">
-        <v>-9.6073</v>
+        <v>-9.6265</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.0139</v>
+        <v>-3.8744</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3291</v>
+        <v>-0.2469</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.6846</v>
+        <v>-3.6277</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1475</v>
+        <v>1.1698</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4425</v>
+        <v>-3.5097</v>
       </c>
       <c r="R13" t="n">
-        <v>4.59</v>
+        <v>4.679399999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9467</v>
+        <v>-1.0196</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.094</v>
+        <v>-1.2665</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1473</v>
+        <v>0.2469</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.4659</v>
+        <v>-2.3968</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.4785</v>
+        <v>-0.5269</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.9873</v>
+        <v>-1.8699</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-47.8721</v>
+        <v>-47.8452</v>
       </c>
       <c r="E14" t="n">
-        <v>-35.8646</v>
+        <v>-40.94</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.0071</v>
+        <v>-6.905600000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-41.9802</v>
+        <v>-41.5739</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.4506</v>
+        <v>-10.0737</v>
       </c>
       <c r="I14" t="n">
-        <v>-31.5291</v>
+        <v>-31.5</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.5441</v>
+        <v>-9.1083</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.0571</v>
+        <v>-7.044599999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.486600000000001</v>
+        <v>-2.064100000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-34.4361</v>
+        <v>-32.4657</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.393199999999999</v>
+        <v>-3.0295</v>
       </c>
       <c r="O14" t="n">
-        <v>-30.0428</v>
+        <v>-29.4364</v>
       </c>
       <c r="P14" t="n">
-        <v>4.59</v>
+        <v>4.679699999999997</v>
       </c>
       <c r="Q14" t="n">
-        <v>-36.7198</v>
+        <v>-37.4359</v>
       </c>
       <c r="R14" t="n">
-        <v>41.31</v>
+        <v>42.1149</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7996</v>
+        <v>-2.3133</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.8485</v>
+        <v>-13.043</v>
       </c>
       <c r="U14" t="n">
-        <v>9.049399999999999</v>
+        <v>10.7299</v>
       </c>
       <c r="V14" t="n">
-        <v>-8.6821</v>
+        <v>-8.637</v>
       </c>
       <c r="W14" t="n">
-        <v>19.24750000000001</v>
+        <v>18.6479</v>
       </c>
       <c r="X14" t="n">
-        <v>-27.9298</v>
+        <v>-27.28430000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4541</v>
+        <v>3.5868</v>
       </c>
       <c r="E2" t="n">
-        <v>3.715100000000001</v>
+        <v>3.7582</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2609</v>
+        <v>-0.1714000000000002</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1924</v>
+        <v>0.2586999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>2.17</v>
+        <v>0.8220999999999998</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0224</v>
+        <v>-0.5634999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9733</v>
+        <v>6.2727</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9815</v>
+        <v>2.5384</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9917</v>
+        <v>3.7343</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7809</v>
+        <v>-6.0139</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1884</v>
+        <v>-1.7161</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.9693</v>
+        <v>-4.297800000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8717</v>
+        <v>0.4641000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1699</v>
+        <v>-6.4981</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0416</v>
+        <v>6.9622</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8509</v>
+        <v>-0.3228999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1524</v>
+        <v>-1.6576</v>
       </c>
       <c r="U2" t="n">
-        <v>2.0035</v>
+        <v>1.3348</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.461</v>
+        <v>3.187</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0641</v>
+        <v>5.6413</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.5251</v>
+        <v>-2.4543</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4037</v>
+        <v>3.5721</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.0614</v>
+        <v>2.4159</v>
       </c>
       <c r="F3" t="n">
-        <v>2.465</v>
+        <v>1.1563</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.1572</v>
+        <v>3.6499</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9473</v>
+        <v>-0.2408</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.1044</v>
+        <v>3.8907</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.8711000000000002</v>
+        <v>5.5049</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7587999999999999</v>
+        <v>-0.1057</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.6299</v>
+        <v>5.6107</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2861</v>
+        <v>-1.8549</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1884999999999999</v>
+        <v>-0.135</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4743</v>
+        <v>-1.72</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2757</v>
+        <v>0.6962</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.6379</v>
+        <v>-1.3924</v>
       </c>
       <c r="R3" t="n">
-        <v>4.9133</v>
+        <v>2.0886</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1424</v>
+        <v>-0.5997</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9491999999999999</v>
+        <v>-1.4434</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8068000000000001</v>
+        <v>0.8438</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4278</v>
+        <v>-0.1743</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3968</v>
+        <v>-0.2532</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.969</v>
+        <v>0.0789</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3262</v>
+        <v>0.02289999999999992</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2187</v>
+        <v>1.0138</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8926</v>
+        <v>-0.991</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.3994</v>
+        <v>-1.4129</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1819</v>
+        <v>0.8361999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.2175</v>
+        <v>-2.2491</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4628000000000001</v>
+        <v>2.4456</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2675</v>
+        <v>2.156</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1953</v>
+        <v>0.2894999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.862200000000001</v>
+        <v>-3.8584</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4494</v>
+        <v>-1.3197</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.4128</v>
+        <v>-2.5386</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5097</v>
+        <v>3.481</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1604</v>
       </c>
       <c r="R4" t="n">
-        <v>3.5097</v>
+        <v>4.641400000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.1044</v>
+        <v>-0.155</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.6288</v>
+        <v>-1.3429</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5243</v>
+        <v>1.188</v>
       </c>
       <c r="V4" t="n">
-        <v>5.3206</v>
+        <v>-1.8903</v>
       </c>
       <c r="W4" t="n">
-        <v>6.3847</v>
+        <v>1.0717</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0641</v>
+        <v>-2.962</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3487999999999998</v>
+        <v>0.01639999999999993</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.3693</v>
+        <v>-0.1795</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7181</v>
+        <v>0.196</v>
       </c>
       <c r="G5" t="n">
-        <v>-5.7576</v>
+        <v>-0.6621</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7078</v>
+        <v>0.8509</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.049799999999999</v>
+        <v>-1.5131</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.6998</v>
+        <v>0.6817</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4924</v>
+        <v>0.7622000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2073999999999998</v>
+        <v>-0.08050000000000002</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.057799999999999</v>
+        <v>-1.3438</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2156000000000001</v>
+        <v>0.0887</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.8424</v>
+        <v>-1.4326</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2338999999999999</v>
+        <v>2.3208</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.3173</v>
+        <v>-0.2321</v>
       </c>
       <c r="R5" t="n">
-        <v>6.5512</v>
+        <v>2.5528</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0541</v>
+        <v>0.2811</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.21</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2641</v>
+        <v>0.1211</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8184</v>
+        <v>-1.9232</v>
       </c>
       <c r="W5" t="n">
-        <v>5.8578</v>
+        <v>-0.789</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0392</v>
+        <v>-1.1341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>R. LOPEZ DE LA TORRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1707999999999998</v>
+        <v>0.0072</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8894</v>
+        <v>-0.1359</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0602</v>
+        <v>0.1432</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3755999999999995</v>
+        <v>-0.3558</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1397</v>
+        <v>-0.1511</v>
       </c>
       <c r="I6" t="n">
-        <v>1.515499999999999</v>
+        <v>-0.2047</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9014</v>
+        <v>0.0168</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6057999999999999</v>
+        <v>0.0168</v>
       </c>
       <c r="L6" t="n">
-        <v>4.507199999999999</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.5258</v>
+        <v>-0.3726</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5341</v>
+        <v>-0.1679</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.9917</v>
+        <v>-0.2047</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9359</v>
+        <v>0.4641</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8076</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7435</v>
+        <v>0.4641</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7729999999999999</v>
+        <v>-0.1011</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.4562</v>
+        <v>-0.1527</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6833</v>
+        <v>0.0516</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3678</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.5268</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7433000000000001</v>
+        <v>-1.988599999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3455</v>
+        <v>2.6632</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6021</v>
+        <v>-4.6517</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3346999999999999</v>
+        <v>0.7464</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05929999999999991</v>
+        <v>3.8278</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3938</v>
+        <v>-3.0813</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4886</v>
+        <v>4.6043</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.02159999999999984</v>
+        <v>4.125999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5099</v>
+        <v>0.4783</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-3.8579</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08079999999999998</v>
+        <v>-0.2982</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9038999999999999</v>
+        <v>-3.5596</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5738</v>
+        <v>-0.4641</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.468</v>
+        <v>-3.4812</v>
       </c>
       <c r="R7" t="n">
-        <v>3.0416</v>
+        <v>3.017</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5777999999999999</v>
+        <v>0.4084</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2252</v>
+        <v>-0.7448999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3527</v>
+        <v>1.1533</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.5602</v>
+        <v>-2.6793</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.591</v>
+        <v>2.2848</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.9692</v>
+        <v>-4.9641</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7133</v>
+        <v>-3.8043</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5511</v>
+        <v>-3.2752</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1622</v>
+        <v>-0.5292</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8899</v>
+        <v>-2.0652</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.534</v>
+        <v>-1.1616</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3557</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1879</v>
+        <v>-0.7796</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08979999999999988</v>
+        <v>-0.8164</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0981</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.0776</v>
+        <v>-1.2856</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6238</v>
+        <v>-0.3452</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.454</v>
+        <v>-0.9405</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4039</v>
+        <v>-3.0169</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9775</v>
+        <v>-3.4811</v>
       </c>
       <c r="R8" t="n">
-        <v>5.3813</v>
+        <v>0.4642</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8061</v>
+        <v>0.2062</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1746000000000001</v>
+        <v>-0.0862</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6315</v>
+        <v>0.2924</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.0333</v>
+        <v>1.0717</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.0974</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.434</v>
+        <v>-3.8375</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.259</v>
+        <v>-1.2943</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.175</v>
+        <v>-2.5432</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.15</v>
+        <v>-2.6059</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.4672000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.141</v>
+        <v>-2.1387</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.5371000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.9973</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.4601000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.15</v>
+        <v>-3.143</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-1.4644</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.141</v>
+        <v>-1.6786</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.2114</v>
+        <v>1.3925</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.6794</v>
+        <v>-1.8566</v>
       </c>
       <c r="R9" t="n">
-        <v>0.468</v>
+        <v>3.2489</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.5937</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5794</v>
+        <v>-1.188</v>
       </c>
       <c r="U9" t="n">
-        <v>0.507</v>
+        <v>0.5942</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.0303</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.213</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.2434</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8848</v>
+        <v>-5.233099999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3404</v>
+        <v>-2.4145</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.5444</v>
+        <v>-2.8186</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8932</v>
+        <v>-6.806799999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5696</v>
+        <v>-1.9797</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6764</v>
+        <v>-4.8269</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8516</v>
+        <v>-2.5623</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5158</v>
+        <v>-0.6832</v>
       </c>
       <c r="L10" t="n">
-        <v>3.3674</v>
+        <v>-1.8791</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.745</v>
+        <v>-4.2445</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0538</v>
+        <v>-1.2965</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.691</v>
+        <v>-2.9479</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3398</v>
+        <v>2.0887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.6794</v>
+        <v>-1.6245</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3398</v>
+        <v>3.713200000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5236</v>
+        <v>-1.874</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.641</v>
+        <v>-1.9786</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1172</v>
+        <v>0.1046</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1282</v>
+        <v>1.3591</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1282</v>
+        <v>3.751</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.2564</v>
+        <v>-2.3919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.815199999999999</v>
+        <v>-6.5227</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.741000000000001</v>
+        <v>-1.8192</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.074400000000001</v>
+        <v>-4.7035</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.2693</v>
+        <v>-3.8854</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.453</v>
+        <v>-1.5674</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8165</v>
+        <v>-2.3179</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.004</v>
+        <v>0.05910000000000004</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4798</v>
+        <v>-0.8538</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4758</v>
+        <v>0.9128999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2655</v>
+        <v>-3.9444</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02679999999999999</v>
+        <v>-0.7136</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2924</v>
+        <v>-3.2308</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9358</v>
+        <v>-2.0887</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.5097</v>
+        <v>-3.4811</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5737</v>
+        <v>1.3925</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1491</v>
+        <v>-0.6901</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3556</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2066</v>
+        <v>-0.008</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.461</v>
+        <v>0.1413</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1283</v>
+        <v>2.2847</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.5891</v>
+        <v>-2.1434</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. HANDS</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.7671</v>
+        <v>-6.7121</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.9435</v>
+        <v>-4.5735</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8235999999999999</v>
+        <v>-2.1387</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.3462</v>
+        <v>-5.3251</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.9648</v>
+        <v>-4.6676</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.381600000000001</v>
+        <v>-0.6576000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.3289</v>
+        <v>-1.7729</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.5832</v>
+        <v>-2.8767</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.7457</v>
+        <v>1.1038</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0173</v>
+        <v>-3.5525</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3814</v>
+        <v>-1.7909</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6359</v>
+        <v>-1.7613</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.8077</v>
+        <v>1.8566</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.6795</v>
+        <v>-3.0169</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8718</v>
+        <v>4.8735</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1823</v>
+        <v>-0.536</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2037</v>
+        <v>-0.8555</v>
       </c>
       <c r="U12" t="n">
-        <v>0.386</v>
+        <v>0.3196</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7955000000000001</v>
+        <v>-2.7075</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2686</v>
+        <v>1.0717</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0641</v>
+        <v>-3.7792</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>J. HANDS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.1911</v>
+        <v>-11.5908</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.3732</v>
+        <v>-8.7873</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8178999999999998</v>
+        <v>-2.8034</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.9444</v>
+        <v>-9.499500000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.6905</v>
+        <v>-2.2167</v>
       </c>
       <c r="I13" t="n">
-        <v>-13.254</v>
+        <v>-7.2828</v>
       </c>
       <c r="J13" t="n">
-        <v>-12.0701</v>
+        <v>-5.214499999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.4436</v>
+        <v>-1.1626</v>
       </c>
       <c r="L13" t="n">
-        <v>-9.6265</v>
+        <v>-4.052</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.8744</v>
+        <v>-4.2849</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2469</v>
+        <v>-1.0541</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.6277</v>
+        <v>-3.2309</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1698</v>
+        <v>-1.3924</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.5097</v>
+        <v>-3.4811</v>
       </c>
       <c r="R13" t="n">
-        <v>4.679399999999999</v>
+        <v>2.0887</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0196</v>
+        <v>0.2316</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2665</v>
+        <v>-0.233</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2469</v>
+        <v>0.4646</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3968</v>
+        <v>-0.9304000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.5269</v>
+        <v>0.1413</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8699</v>
+        <v>-1.0717</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,145 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-47.8452</v>
+        <v>-15.1999</v>
       </c>
       <c r="E14" t="n">
-        <v>-40.94</v>
+        <v>-14.0427</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.905600000000001</v>
+        <v>-1.1572</v>
       </c>
       <c r="G14" t="n">
-        <v>-41.5739</v>
+        <v>-11.6177</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.0737</v>
+        <v>-3.2609</v>
       </c>
       <c r="I14" t="n">
-        <v>-31.5</v>
+        <v>-8.357000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.1083</v>
+        <v>-5.8945</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.044599999999999</v>
+        <v>-1.302</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.064100000000001</v>
+        <v>-4.5927</v>
       </c>
       <c r="M14" t="n">
-        <v>-32.4657</v>
+        <v>-5.7232</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.0295</v>
+        <v>-1.959</v>
       </c>
       <c r="O14" t="n">
-        <v>-29.4364</v>
+        <v>-3.7643</v>
       </c>
       <c r="P14" t="n">
-        <v>4.679699999999997</v>
+        <v>-1.1604</v>
       </c>
       <c r="Q14" t="n">
-        <v>-37.4359</v>
+        <v>-7.4264</v>
       </c>
       <c r="R14" t="n">
-        <v>42.1149</v>
+        <v>6.2659</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3133</v>
+        <v>-2.0613</v>
       </c>
       <c r="T14" t="n">
-        <v>-13.043</v>
+        <v>-2.1057</v>
       </c>
       <c r="U14" t="n">
-        <v>10.7299</v>
+        <v>0.04429999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-8.637</v>
+        <v>-0.3603000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>18.6479</v>
+        <v>1.3838</v>
       </c>
       <c r="X14" t="n">
-        <v>-27.28430000000001</v>
+        <v>-1.7443</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UCAM Murcia</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-47.6836</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-26.671</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-21.0124</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-39.5814</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-9.376000000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-30.2056</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.898400000000001</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.796299999999999</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.101900000000001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-43.4796</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-12.1719</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-31.30759999999999</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.6415</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-37.1319</v>
+      </c>
+      <c r="R15" t="n">
+        <v>41.773</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-5.8065</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-12.3105</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6.5043</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-6.936500000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>18.87280000000001</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-25.8095</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
@@ -565,67 +565,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5868</v>
+        <v>3.6198</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7582</v>
+        <v>3.5025</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1714000000000002</v>
+        <v>0.1173000000000002</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2586999999999999</v>
+        <v>0.3027000000000005</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8220999999999998</v>
+        <v>0.9087000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5634999999999999</v>
+        <v>-0.6059</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2727</v>
+        <v>6.086</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5384</v>
+        <v>2.4638</v>
       </c>
       <c r="L2" t="n">
-        <v>3.7343</v>
+        <v>3.622199999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-6.0139</v>
+        <v>-5.7832</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7161</v>
+        <v>-1.5551</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.297800000000001</v>
+        <v>-4.2282</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4641000000000001</v>
+        <v>0.4675</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.4981</v>
+        <v>-6.545400000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>6.9622</v>
+        <v>7.013</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3228999999999999</v>
+        <v>-0.3180999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.6576</v>
+        <v>-1.6328</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3348</v>
+        <v>1.3146</v>
       </c>
       <c r="V2" t="n">
-        <v>3.187</v>
+        <v>3.1678</v>
       </c>
       <c r="W2" t="n">
-        <v>5.6413</v>
+        <v>5.5948</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4543</v>
+        <v>-2.427</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5721</v>
+        <v>3.4648</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4159</v>
+        <v>2.1708</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1563</v>
+        <v>1.294</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6499</v>
+        <v>3.5484</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2408</v>
+        <v>-0.2579</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8907</v>
+        <v>3.8064</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5049</v>
+        <v>5.271</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1057</v>
+        <v>-0.2191</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6107</v>
+        <v>5.49</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8549</v>
+        <v>-1.7225</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.135</v>
+        <v>-0.03889999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.72</v>
+        <v>-1.6836</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6962</v>
+        <v>0.7013</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3924</v>
+        <v>-1.4026</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0886</v>
+        <v>2.1039</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5997</v>
+        <v>-0.6021</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4434</v>
+        <v>-1.4353</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8438</v>
+        <v>0.8331000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1743</v>
+        <v>-0.1829</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2532</v>
+        <v>-0.2623</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0789</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02289999999999992</v>
+        <v>0.1273000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0138</v>
+        <v>0.9038999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.991</v>
+        <v>-0.7765</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4129</v>
+        <v>-1.3592</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8361999999999999</v>
+        <v>0.9127000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2491</v>
+        <v>-2.272</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4456</v>
+        <v>2.335</v>
       </c>
       <c r="K4" t="n">
-        <v>2.156</v>
+        <v>2.1179</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2894999999999999</v>
+        <v>0.2171000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.8584</v>
+        <v>-3.6942</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3197</v>
+        <v>-1.2052</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.5386</v>
+        <v>-2.489</v>
       </c>
       <c r="P4" t="n">
-        <v>3.481</v>
+        <v>3.5065</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1604</v>
+        <v>-1.1688</v>
       </c>
       <c r="R4" t="n">
-        <v>4.641400000000001</v>
+        <v>4.6754</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.155</v>
+        <v>-0.1523</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3429</v>
+        <v>-1.3272</v>
       </c>
       <c r="U4" t="n">
-        <v>1.188</v>
+        <v>1.1749</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8903</v>
+        <v>-1.8675</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0717</v>
+        <v>1.0649</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.962</v>
+        <v>-2.9325</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01639999999999993</v>
+        <v>0.0901000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1795</v>
+        <v>-0.2074</v>
       </c>
       <c r="F5" t="n">
-        <v>0.196</v>
+        <v>0.2975</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6621</v>
+        <v>-0.6197</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8509</v>
+        <v>0.8815999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5131</v>
+        <v>-1.5014</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6817</v>
+        <v>0.6461</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7622000000000001</v>
+        <v>0.7382000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.08050000000000002</v>
+        <v>-0.09200000000000008</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3438</v>
+        <v>-1.2659</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0887</v>
+        <v>0.1435</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4326</v>
+        <v>-1.4094</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3208</v>
+        <v>2.3377</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2321</v>
+        <v>-0.2338</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5528</v>
+        <v>2.5715</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2811</v>
+        <v>0.2875</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.175</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1211</v>
+        <v>0.1126</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9232</v>
+        <v>-1.9154</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.789</v>
+        <v>-0.7948</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1341</v>
+        <v>-1.1206</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0072</v>
+        <v>0.0164</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1359</v>
+        <v>-0.1352</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1432</v>
+        <v>0.1516</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3558</v>
+        <v>-0.351</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1511</v>
+        <v>-0.1496</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2047</v>
+        <v>-0.2013</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0168</v>
+        <v>0.0166</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0168</v>
+        <v>0.0166</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3726</v>
+        <v>-0.3676</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1679</v>
+        <v>-0.1662</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2047</v>
+        <v>-0.2013</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4641</v>
+        <v>0.4675</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4641</v>
+        <v>0.4675</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1011</v>
+        <v>-0.1002</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1527</v>
+        <v>-0.1518</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0516</v>
+        <v>0.0517</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,73 +955,73 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.988599999999999</v>
+        <v>-1.992699999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6632</v>
+        <v>2.4712</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.6517</v>
+        <v>-4.4639</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7464</v>
+        <v>0.7276000000000002</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8278</v>
+        <v>3.7663</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0813</v>
+        <v>-3.0386</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6043</v>
+        <v>4.446099999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>4.125999999999999</v>
+        <v>3.9701</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4783</v>
+        <v>0.4762</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.8579</v>
+        <v>-3.7186</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2982</v>
+        <v>-0.2038</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.5596</v>
+        <v>-3.5148</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4641</v>
+        <v>-0.4675</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4812</v>
+        <v>-3.5064</v>
       </c>
       <c r="R7" t="n">
-        <v>3.017</v>
+        <v>3.0389</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4084</v>
+        <v>0.4095</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7448999999999999</v>
+        <v>-0.7333999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1533</v>
+        <v>1.1431</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.6793</v>
+        <v>-2.6624</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2848</v>
+        <v>2.2649</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.9641</v>
+        <v>-4.9272</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8043</v>
+        <v>-3.8032</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2752</v>
+        <v>-1.427</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5292</v>
+        <v>-2.3763</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0652</v>
+        <v>-2.5939</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1616</v>
+        <v>-0.3939000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-2.2</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7796</v>
+        <v>0.4180999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8164</v>
+        <v>0.9709000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>-0.5528000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2856</v>
+        <v>-3.0119</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3452</v>
+        <v>-1.3647</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9405</v>
+        <v>-1.6472</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.0169</v>
+        <v>1.4026</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4811</v>
+        <v>-1.8701</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4642</v>
+        <v>3.2727</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2062</v>
+        <v>-0.59</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0862</v>
+        <v>-1.1749</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2924</v>
+        <v>0.5847</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0717</v>
+        <v>-2.0218</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0717</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.2218</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8375</v>
+        <v>-3.8215</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2943</v>
+        <v>-3.3128</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5432</v>
+        <v>-0.5087</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6059</v>
+        <v>-2.0568</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4672000000000001</v>
+        <v>-1.1596</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1387</v>
+        <v>-0.8972</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5371000000000001</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9973</v>
+        <v>-0.8245</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4601000000000001</v>
+        <v>0.0366</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.143</v>
+        <v>-1.2689</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4644</v>
+        <v>-0.3351</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6786</v>
+        <v>-0.9338</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3925</v>
+        <v>-3.039</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8566</v>
+        <v>-3.5065</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2489</v>
+        <v>0.4676</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5937</v>
+        <v>0.2093</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.188</v>
+        <v>-0.08350000000000002</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5942</v>
+        <v>0.2928</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.0303</v>
+        <v>1.0649</v>
       </c>
       <c r="W9" t="n">
-        <v>1.213</v>
+        <v>1.0649</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.2434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.233099999999999</v>
+        <v>-5.2902</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4145</v>
+        <v>-2.6563</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8186</v>
+        <v>-2.634</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.806799999999999</v>
+        <v>-6.8653</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9797</v>
+        <v>-1.9728</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.8269</v>
+        <v>-4.8925</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.5623</v>
+        <v>-2.7752</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6832</v>
+        <v>-0.7743</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8791</v>
+        <v>-2.0008</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.2445</v>
+        <v>-4.0901</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2965</v>
+        <v>-1.1985</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.9479</v>
+        <v>-2.8917</v>
       </c>
       <c r="P10" t="n">
-        <v>2.0887</v>
+        <v>2.1038</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.6245</v>
+        <v>-1.6364</v>
       </c>
       <c r="R10" t="n">
-        <v>3.713200000000001</v>
+        <v>3.7402</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.874</v>
+        <v>-1.8848</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.9786</v>
+        <v>-1.9722</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1046</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3591</v>
+        <v>1.3558</v>
       </c>
       <c r="W10" t="n">
-        <v>3.751</v>
+        <v>3.7272</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3919</v>
+        <v>-2.3714</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5227</v>
+        <v>-6.5391</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8192</v>
+        <v>-1.9155</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.7035</v>
+        <v>-4.6236</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8854</v>
+        <v>-3.8785</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5674</v>
+        <v>-1.5711</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3179</v>
+        <v>-2.3073</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05910000000000004</v>
+        <v>0.002700000000000036</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8538</v>
+        <v>-0.8942</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9128999999999999</v>
+        <v>0.8969000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.9444</v>
+        <v>-3.8811</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7136</v>
+        <v>-0.677</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.2308</v>
+        <v>-3.2041</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0887</v>
+        <v>-2.1039</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4811</v>
+        <v>-3.5065</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3925</v>
+        <v>1.4026</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6901</v>
+        <v>-0.6919000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6767000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.008</v>
+        <v>-0.0152</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1413</v>
+        <v>0.1351</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2847</v>
+        <v>2.2649</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1434</v>
+        <v>-2.1299</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7121</v>
+        <v>-6.625999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5735</v>
+        <v>-4.670199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1387</v>
+        <v>-1.9558</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.3251</v>
+        <v>-5.2777</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.6676</v>
+        <v>-4.6563</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6576000000000001</v>
+        <v>-0.6214000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7729</v>
+        <v>-1.8631</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.8767</v>
+        <v>-2.9619</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1038</v>
+        <v>1.0988</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.5525</v>
+        <v>-3.4146</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7909</v>
+        <v>-1.6945</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7613</v>
+        <v>-1.7201</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8566</v>
+        <v>1.8702</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0169</v>
+        <v>-3.0389</v>
       </c>
       <c r="R12" t="n">
-        <v>4.8735</v>
+        <v>4.9091</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.536</v>
+        <v>-0.5289</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8555</v>
+        <v>-0.833</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3196</v>
+        <v>0.304</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7075</v>
+        <v>-2.6894</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0717</v>
+        <v>1.0649</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.7792</v>
+        <v>-3.7544</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.5908</v>
+        <v>-11.5963</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.7873</v>
+        <v>-8.8825</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8034</v>
+        <v>-2.7137</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.499500000000001</v>
+        <v>-9.502800000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.2167</v>
+        <v>-2.1943</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.2828</v>
+        <v>-7.3085</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.214499999999999</v>
+        <v>-5.2879</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1626</v>
+        <v>-1.1834</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.052</v>
+        <v>-4.1045</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.2849</v>
+        <v>-4.2149</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0541</v>
+        <v>-1.0109</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.2309</v>
+        <v>-3.2041</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3924</v>
+        <v>-1.4027</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4811</v>
+        <v>-3.5065</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0887</v>
+        <v>2.1039</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2316</v>
+        <v>0.239</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.233</v>
+        <v>-0.2232</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4646</v>
+        <v>0.4623</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9304000000000001</v>
+        <v>-0.9298</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1413</v>
+        <v>0.1351</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0717</v>
+        <v>-1.0649</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.1999</v>
+        <v>-15.3679</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.0427</v>
+        <v>-14.4196</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1572</v>
+        <v>-0.9482999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-11.6177</v>
+        <v>-11.762</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.2609</v>
+        <v>-3.2966</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.357000000000001</v>
+        <v>-8.4655</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.8945</v>
+        <v>-6.1851</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.302</v>
+        <v>-1.4357</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.5927</v>
+        <v>-4.7493</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.7232</v>
+        <v>-5.5769</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.959</v>
+        <v>-1.8607</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7643</v>
+        <v>-3.7161</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1604</v>
+        <v>-1.1688</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.4264</v>
+        <v>-7.4804</v>
       </c>
       <c r="R14" t="n">
-        <v>6.2659</v>
+        <v>6.3117</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0613</v>
+        <v>-2.0683</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.1057</v>
+        <v>-2.0968</v>
       </c>
       <c r="U14" t="n">
-        <v>0.04429999999999999</v>
+        <v>0.0285</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3603000000000001</v>
+        <v>-0.3688999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3838</v>
+        <v>1.3428</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7443</v>
+        <v>-1.7117</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-47.6836</v>
+        <v>-47.7185</v>
       </c>
       <c r="E15" t="n">
-        <v>-26.671</v>
+        <v>-28.5781</v>
       </c>
       <c r="F15" t="n">
-        <v>-21.0124</v>
+        <v>-19.1404</v>
       </c>
       <c r="G15" t="n">
-        <v>-39.5814</v>
+        <v>-39.6882</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.376000000000001</v>
+        <v>-9.182799999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-30.2056</v>
+        <v>-30.5052</v>
       </c>
       <c r="J15" t="n">
-        <v>3.898400000000001</v>
+        <v>2.3225</v>
       </c>
       <c r="K15" t="n">
-        <v>2.796299999999999</v>
+        <v>1.984399999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>1.101900000000001</v>
+        <v>0.3384</v>
       </c>
       <c r="M15" t="n">
-        <v>-43.4796</v>
+        <v>-42.0104</v>
       </c>
       <c r="N15" t="n">
-        <v>-12.1719</v>
+        <v>-11.1671</v>
       </c>
       <c r="O15" t="n">
-        <v>-31.30759999999999</v>
+        <v>-30.8434</v>
       </c>
       <c r="P15" t="n">
-        <v>4.6415</v>
+        <v>4.675199999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-37.1319</v>
+        <v>-37.4023</v>
       </c>
       <c r="R15" t="n">
-        <v>41.773</v>
+        <v>42.07800000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.8065</v>
+        <v>-5.7913</v>
       </c>
       <c r="T15" t="n">
-        <v>-12.3105</v>
+        <v>-12.1658</v>
       </c>
       <c r="U15" t="n">
-        <v>6.5043</v>
+        <v>6.374600000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.936500000000001</v>
+        <v>-6.9145</v>
       </c>
       <c r="W15" t="n">
-        <v>18.87280000000001</v>
+        <v>18.6673</v>
       </c>
       <c r="X15" t="n">
-        <v>-25.8095</v>
+        <v>-25.5819</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
@@ -565,67 +565,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6198</v>
+        <v>3.6102</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5025</v>
+        <v>3.4594</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1173000000000002</v>
+        <v>0.1509</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3027000000000005</v>
+        <v>0.3025000000000005</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9087000000000001</v>
+        <v>0.9036</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6059</v>
+        <v>-0.6011000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>6.086</v>
+        <v>6.093</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4638</v>
+        <v>2.4632</v>
       </c>
       <c r="L2" t="n">
-        <v>3.622199999999999</v>
+        <v>3.6299</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.7832</v>
+        <v>-5.7905</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5551</v>
+        <v>-1.5595</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.2282</v>
+        <v>-4.231</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4675</v>
+        <v>0.4679</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.545400000000001</v>
+        <v>-6.5505</v>
       </c>
       <c r="R2" t="n">
-        <v>7.013</v>
+        <v>7.0185</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3180999999999999</v>
+        <v>-0.3258999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.6328</v>
+        <v>-1.6729</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3146</v>
+        <v>1.3471</v>
       </c>
       <c r="V2" t="n">
-        <v>3.1678</v>
+        <v>3.1657</v>
       </c>
       <c r="W2" t="n">
-        <v>5.5948</v>
+        <v>5.5898</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.427</v>
+        <v>-2.4241</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4648</v>
+        <v>3.4677</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1708</v>
+        <v>2.1598</v>
       </c>
       <c r="F3" t="n">
-        <v>1.294</v>
+        <v>1.308</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5484</v>
+        <v>3.5544</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2579</v>
+        <v>-0.2569</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8064</v>
+        <v>3.8111</v>
       </c>
       <c r="J3" t="n">
-        <v>5.271</v>
+        <v>5.2828</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2191</v>
+        <v>-0.2139</v>
       </c>
       <c r="L3" t="n">
-        <v>5.49</v>
+        <v>5.496799999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7225</v>
+        <v>-1.7285</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.03889999999999999</v>
+        <v>-0.04289999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6836</v>
+        <v>-1.6857</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7013</v>
+        <v>0.7018</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.4026</v>
+        <v>-1.4037</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1039</v>
+        <v>2.1055</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6021</v>
+        <v>-0.6046</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4353</v>
+        <v>-1.456</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8331000000000001</v>
+        <v>0.8513999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1829</v>
+        <v>-0.1838</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2623</v>
+        <v>-0.2633</v>
       </c>
       <c r="X3" t="n">
         <v>0.0795</v>
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1273000000000001</v>
+        <v>0.1283</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9038999999999999</v>
+        <v>0.8797000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7765</v>
+        <v>-0.7514</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3592</v>
+        <v>-1.3593</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9127000000000001</v>
+        <v>0.9080999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.272</v>
+        <v>-2.2674</v>
       </c>
       <c r="J4" t="n">
-        <v>2.335</v>
+        <v>2.3403</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1179</v>
+        <v>2.1163</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2171000000000001</v>
+        <v>0.2240999999999998</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.6942</v>
+        <v>-3.6996</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2052</v>
+        <v>-1.2081</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.489</v>
+        <v>-2.4915</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5065</v>
+        <v>3.5092</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1688</v>
+        <v>-1.1697</v>
       </c>
       <c r="R4" t="n">
-        <v>4.6754</v>
+        <v>4.678900000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1523</v>
+        <v>-0.1565</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3272</v>
+        <v>-1.3552</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1749</v>
+        <v>1.1986</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8675</v>
+        <v>-1.8651</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0649</v>
+        <v>1.0642</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.9325</v>
+        <v>-2.9293</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0901000000000001</v>
+        <v>0.08609999999999998</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2074</v>
+        <v>-0.2215</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2975</v>
+        <v>0.3075</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6197</v>
+        <v>-0.6222000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8815999999999999</v>
+        <v>0.879</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5014</v>
+        <v>-1.5012</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6461</v>
+        <v>0.6472000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7382000000000001</v>
+        <v>0.7380000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.09200000000000008</v>
+        <v>-0.0907</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2659</v>
+        <v>-1.2694</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1435</v>
+        <v>0.1409</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4094</v>
+        <v>-1.4104</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3377</v>
+        <v>2.3394</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2338</v>
+        <v>-0.2339</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5715</v>
+        <v>2.5734</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2875</v>
+        <v>0.2832</v>
       </c>
       <c r="T5" t="n">
-        <v>0.175</v>
+        <v>0.1606</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1126</v>
+        <v>0.1225</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9154</v>
+        <v>-1.9145</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7948</v>
+        <v>-0.7954</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1206</v>
+        <v>-1.1191</v>
       </c>
     </row>
     <row r="6">
@@ -877,22 +877,22 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0164</v>
+        <v>0.0149</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1352</v>
+        <v>-0.1375</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1516</v>
+        <v>0.1524</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.351</v>
+        <v>-0.3509</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1496</v>
+        <v>-0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2013</v>
+        <v>-0.2015</v>
       </c>
       <c r="J6" t="n">
         <v>0.0166</v>
@@ -904,31 +904,31 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3676</v>
+        <v>-0.3675</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1662</v>
+        <v>-0.1661</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2013</v>
+        <v>-0.2015</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4675</v>
+        <v>0.4679</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4675</v>
+        <v>0.4679</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1002</v>
+        <v>-0.102</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1518</v>
+        <v>-0.1541</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0517</v>
+        <v>0.052</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.992699999999999</v>
+        <v>-1.9935</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4712</v>
+        <v>2.448300000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.4639</v>
+        <v>-4.441800000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7276000000000002</v>
+        <v>0.7231000000000003</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7663</v>
+        <v>3.763</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0386</v>
+        <v>-3.04</v>
       </c>
       <c r="J7" t="n">
-        <v>4.446099999999999</v>
+        <v>4.446400000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9701</v>
+        <v>3.9706</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4762</v>
+        <v>0.4758</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.7186</v>
+        <v>-3.7232</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2038</v>
+        <v>-0.2074</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.5148</v>
+        <v>-3.5159</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4675</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.5064</v>
+        <v>-3.5091</v>
       </c>
       <c r="R7" t="n">
-        <v>3.0389</v>
+        <v>3.0412</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4095</v>
+        <v>0.4118</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7333999999999999</v>
+        <v>-0.7517999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1431</v>
+        <v>1.1636</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.6624</v>
+        <v>-2.6605</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2649</v>
+        <v>2.2628</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.9272</v>
+        <v>-4.9233</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8032</v>
+        <v>-3.8043</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.427</v>
+        <v>-1.4442</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3763</v>
+        <v>-2.3601</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5939</v>
+        <v>-2.5881</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3939000000000001</v>
+        <v>-0.3964</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2</v>
+        <v>-2.1919</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4180999999999999</v>
+        <v>0.4273999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9709000000000001</v>
+        <v>0.9705</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5528000000000001</v>
+        <v>-0.543</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.0119</v>
+        <v>-3.0155</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3647</v>
+        <v>-1.3669</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6472</v>
+        <v>-1.6487</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4026</v>
+        <v>1.4037</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8701</v>
+        <v>-1.8715</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2727</v>
+        <v>3.2752</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.59</v>
+        <v>-0.599</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1749</v>
+        <v>-1.1987</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5847</v>
+        <v>0.5997</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.0218</v>
+        <v>-2.0209</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.1986</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.2218</v>
+        <v>-3.2195</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8215</v>
+        <v>-3.8243</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3128</v>
+        <v>-3.3184</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5087</v>
+        <v>-0.5059</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0568</v>
+        <v>-2.0549</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1596</v>
+        <v>-1.1579</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8972</v>
+        <v>-0.8969</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.7863</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8245</v>
+        <v>-0.8229</v>
       </c>
       <c r="L9" t="n">
         <v>0.0366</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2689</v>
+        <v>-1.2686</v>
       </c>
       <c r="N9" t="n">
         <v>-0.3351</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9338</v>
+        <v>-0.9336</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.039</v>
+        <v>-3.0413</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.5065</v>
+        <v>-3.5092</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4676</v>
+        <v>0.4678</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2093</v>
+        <v>0.2077</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.08350000000000002</v>
+        <v>-0.08710000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2928</v>
+        <v>0.2948</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0649</v>
+        <v>1.0642</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0649</v>
+        <v>1.0642</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2902</v>
+        <v>-5.2796</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6563</v>
+        <v>-2.6647</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.634</v>
+        <v>-2.6149</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.8653</v>
+        <v>-6.8514</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9728</v>
+        <v>-1.9701</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.8925</v>
+        <v>-4.8813</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7752</v>
+        <v>-2.7561</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7743</v>
+        <v>-0.7692</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0008</v>
+        <v>-1.9868</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.0901</v>
+        <v>-4.0953</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1985</v>
+        <v>-1.2008</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.8917</v>
+        <v>-2.8944</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1038</v>
+        <v>2.1055</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.6364</v>
+        <v>-1.6376</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7402</v>
+        <v>3.7431</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8848</v>
+        <v>-1.8893</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.9722</v>
+        <v>-1.9957</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1064</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3558</v>
+        <v>1.3555</v>
       </c>
       <c r="W10" t="n">
-        <v>3.7272</v>
+        <v>3.7247</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3714</v>
+        <v>-2.3692</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5391</v>
+        <v>-6.5416</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9155</v>
+        <v>-1.928</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.6236</v>
+        <v>-4.6137</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8785</v>
+        <v>-3.8747</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5711</v>
+        <v>-1.5686</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3073</v>
+        <v>-2.3061</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002700000000000036</v>
+        <v>0.006500000000000061</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8942</v>
+        <v>-0.8912</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8969000000000001</v>
+        <v>0.8975</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.8811</v>
+        <v>-3.8812</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.677</v>
+        <v>-0.6775</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.2041</v>
+        <v>-3.2037</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1039</v>
+        <v>-2.1055</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.5065</v>
+        <v>-3.5092</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4026</v>
+        <v>1.4036</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6919000000000001</v>
+        <v>-0.6958</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6767000000000001</v>
+        <v>-0.6880999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0152</v>
+        <v>-0.007699999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1351</v>
+        <v>0.1344000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2649</v>
+        <v>2.2628</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1299</v>
+        <v>-2.1284</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.625999999999999</v>
+        <v>-6.630800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.670199999999999</v>
+        <v>-4.6966</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9558</v>
+        <v>-1.9342</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.2777</v>
+        <v>-5.2741</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.6563</v>
+        <v>-4.6497</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6214000000000001</v>
+        <v>-0.6244000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8631</v>
+        <v>-1.8557</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.9619</v>
+        <v>-2.9538</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0988</v>
+        <v>1.0981</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.4146</v>
+        <v>-3.4186</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6945</v>
+        <v>-1.6959</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7201</v>
+        <v>-1.7225</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8702</v>
+        <v>1.8716</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0389</v>
+        <v>-3.0413</v>
       </c>
       <c r="R12" t="n">
-        <v>4.9091</v>
+        <v>4.9129</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5289</v>
+        <v>-0.5408000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.833</v>
+        <v>-0.8639</v>
       </c>
       <c r="U12" t="n">
-        <v>0.304</v>
+        <v>0.3229</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.6894</v>
+        <v>-2.6874</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0649</v>
+        <v>1.0642</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.7544</v>
+        <v>-3.7516</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.5963</v>
+        <v>-11.5911</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.8825</v>
+        <v>-8.8863</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7137</v>
+        <v>-2.7048</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.502800000000001</v>
+        <v>-9.4909</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1943</v>
+        <v>-2.1919</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.3085</v>
+        <v>-7.298999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.2879</v>
+        <v>-5.2761</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1834</v>
+        <v>-1.1808</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.1045</v>
+        <v>-4.0953</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.2149</v>
+        <v>-4.2147</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0109</v>
+        <v>-1.0111</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.2041</v>
+        <v>-3.2038</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.4027</v>
+        <v>-1.4037</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.5065</v>
+        <v>-3.5092</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1039</v>
+        <v>2.1055</v>
       </c>
       <c r="S13" t="n">
-        <v>0.239</v>
+        <v>0.2331</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2232</v>
+        <v>-0.2355</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4623</v>
+        <v>0.4686</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9298</v>
+        <v>-0.9298000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1351</v>
+        <v>0.1344</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0649</v>
+        <v>-1.0642</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.3679</v>
+        <v>-15.3545</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.4196</v>
+        <v>-14.429</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9482999999999999</v>
+        <v>-0.9255</v>
       </c>
       <c r="G14" t="n">
-        <v>-11.762</v>
+        <v>-11.7365</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.2966</v>
+        <v>-3.29</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.4655</v>
+        <v>-8.446400000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.1851</v>
+        <v>-6.157100000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.4357</v>
+        <v>-1.4279</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.7493</v>
+        <v>-4.7291</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.5769</v>
+        <v>-5.5793</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8607</v>
+        <v>-1.862</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7161</v>
+        <v>-3.7173</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1688</v>
+        <v>-1.1698</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.4804</v>
+        <v>-7.4863</v>
       </c>
       <c r="R14" t="n">
-        <v>6.3117</v>
+        <v>6.3166</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0683</v>
+        <v>-2.0785</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.0968</v>
+        <v>-2.1239</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0285</v>
+        <v>0.04549999999999998</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3688999999999999</v>
+        <v>-0.3696999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3428</v>
+        <v>1.3385</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7117</v>
+        <v>-1.7082</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-47.7185</v>
+        <v>-47.7125</v>
       </c>
       <c r="E15" t="n">
-        <v>-28.5781</v>
+        <v>-28.779</v>
       </c>
       <c r="F15" t="n">
-        <v>-19.1404</v>
+        <v>-18.9335</v>
       </c>
       <c r="G15" t="n">
-        <v>-39.6882</v>
+        <v>-39.623</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.182799999999999</v>
+        <v>-9.177199999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-30.5052</v>
+        <v>-30.4461</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3225</v>
+        <v>2.428900000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>1.984399999999999</v>
+        <v>2.015500000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3384</v>
+        <v>0.4139000000000008</v>
       </c>
       <c r="M15" t="n">
-        <v>-42.0104</v>
+        <v>-42.0519</v>
       </c>
       <c r="N15" t="n">
-        <v>-11.1671</v>
+        <v>-11.1924</v>
       </c>
       <c r="O15" t="n">
-        <v>-30.8434</v>
+        <v>-30.86</v>
       </c>
       <c r="P15" t="n">
-        <v>4.675199999999999</v>
+        <v>4.678799999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-37.4023</v>
+        <v>-37.4312</v>
       </c>
       <c r="R15" t="n">
-        <v>42.07800000000001</v>
+        <v>42.1101</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.7913</v>
+        <v>-5.8566</v>
       </c>
       <c r="T15" t="n">
-        <v>-12.1658</v>
+        <v>-12.4223</v>
       </c>
       <c r="U15" t="n">
-        <v>6.374600000000001</v>
+        <v>6.5654</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.9145</v>
+        <v>-6.911900000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>18.6673</v>
+        <v>18.6455</v>
       </c>
       <c r="X15" t="n">
-        <v>-25.5819</v>
+        <v>-25.5574</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,122 +417,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total_NP</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Off_NP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Def_NP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Net_Shooting</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Net_2P</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net_3P</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Off_Shooting</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Off_2P</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Off_3P</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Def_Shooting</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Def_2P</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Def_3P</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Net_TOV</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Off_TOV</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Def_TOV</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Net_ORB</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Off_ORB</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Def_ORB</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Net_FT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Off_FT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Def_FT</t>
         </is>
@@ -565,67 +553,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6102</v>
+        <v>3.6079</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4594</v>
+        <v>3.4541</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1509</v>
+        <v>0.1538999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3025000000000005</v>
+        <v>0.3018999999999997</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9036</v>
+        <v>0.9015</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6011000000000001</v>
+        <v>-0.5997000000000002</v>
       </c>
       <c r="J2" t="n">
-        <v>6.093</v>
+        <v>6.0968</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4632</v>
+        <v>2.4639</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6299</v>
+        <v>3.6327</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.7905</v>
+        <v>-5.7948</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5595</v>
+        <v>-1.5624</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.231</v>
+        <v>-4.2325</v>
       </c>
       <c r="P2" t="n">
         <v>0.4679</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.5505</v>
+        <v>-6.551</v>
       </c>
       <c r="R2" t="n">
-        <v>7.0185</v>
+        <v>7.018899999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3258999999999999</v>
+        <v>-0.3275</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.6729</v>
+        <v>-1.681</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3471</v>
+        <v>1.3537</v>
       </c>
       <c r="V2" t="n">
-        <v>3.1657</v>
+        <v>3.1656</v>
       </c>
       <c r="W2" t="n">
-        <v>5.5898</v>
+        <v>5.589399999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4241</v>
+        <v>-2.4239</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +631,64 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4677</v>
+        <v>3.4697</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1598</v>
+        <v>2.1607</v>
       </c>
       <c r="F3" t="n">
-        <v>1.308</v>
+        <v>1.309</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5544</v>
+        <v>3.5567</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2569</v>
+        <v>-0.2563</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8111</v>
+        <v>3.8131</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2828</v>
+        <v>5.288</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2139</v>
+        <v>-0.2115</v>
       </c>
       <c r="L3" t="n">
-        <v>5.496799999999999</v>
+        <v>5.4996</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7285</v>
+        <v>-1.7313</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.04289999999999999</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6857</v>
+        <v>-1.6864</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7018</v>
+        <v>0.7019</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.4037</v>
+        <v>-1.4038</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1055</v>
+        <v>2.1056</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6046</v>
+        <v>-0.605</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.456</v>
+        <v>-1.4602</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8513999999999999</v>
+        <v>0.855</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1838</v>
+        <v>-0.1839</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2633</v>
+        <v>-0.2634</v>
       </c>
       <c r="X3" t="n">
         <v>0.0795</v>
@@ -721,67 +709,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1283</v>
+        <v>0.1271999999999998</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8797000000000001</v>
+        <v>0.8764000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7514</v>
+        <v>-0.7491000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3593</v>
+        <v>-1.3601</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9080999999999999</v>
+        <v>0.9062</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2674</v>
+        <v>-2.2662</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3403</v>
+        <v>2.3428</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1163</v>
+        <v>2.1164</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2240999999999998</v>
+        <v>0.2263000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.6996</v>
+        <v>-3.7029</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2081</v>
+        <v>-1.2103</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4915</v>
+        <v>-2.4927</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5092</v>
+        <v>3.5094</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1697</v>
+        <v>-1.1698</v>
       </c>
       <c r="R4" t="n">
-        <v>4.678900000000001</v>
+        <v>4.6792</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1565</v>
+        <v>-0.1574</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3552</v>
+        <v>-1.3608</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1986</v>
+        <v>1.2035</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8651</v>
+        <v>-1.8649</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0642</v>
+        <v>1.0641</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.9293</v>
+        <v>-2.929</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +787,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08609999999999998</v>
+        <v>0.0844</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2215</v>
+        <v>-0.2238</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3075</v>
+        <v>0.3081999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6222000000000001</v>
+        <v>-0.6231000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.879</v>
+        <v>0.8779999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5012</v>
+        <v>-1.5011</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6472000000000001</v>
+        <v>0.6479</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7380000000000001</v>
+        <v>0.7383000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0907</v>
+        <v>-0.09030000000000005</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2694</v>
+        <v>-1.2711</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1409</v>
+        <v>0.1398</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4104</v>
+        <v>-1.4108</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3394</v>
+        <v>2.3397</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2339</v>
+        <v>-0.234</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5734</v>
+        <v>2.5737</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2832</v>
+        <v>0.2822</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1606</v>
+        <v>0.1577</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1225</v>
+        <v>0.1246</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9145</v>
+        <v>-1.9144</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7954</v>
+        <v>-0.7955</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1191</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="6">
@@ -877,16 +865,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0149</v>
+        <v>0.0145</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1375</v>
+        <v>-0.1379</v>
       </c>
       <c r="F6" t="n">
         <v>0.1524</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3509</v>
+        <v>-0.351</v>
       </c>
       <c r="H6" t="n">
         <v>-0.1494</v>
@@ -904,10 +892,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3675</v>
+        <v>-0.3676</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1661</v>
+        <v>-0.166</v>
       </c>
       <c r="O6" t="n">
         <v>-0.2015</v>
@@ -922,13 +910,13 @@
         <v>0.4679</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.102</v>
+        <v>-0.1024</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1541</v>
+        <v>-0.1545</v>
       </c>
       <c r="U6" t="n">
-        <v>0.052</v>
+        <v>0.0521</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +943,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9935</v>
+        <v>-1.9936</v>
       </c>
       <c r="E7" t="n">
-        <v>2.448300000000001</v>
+        <v>2.4462</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.441800000000001</v>
+        <v>-4.4397</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7231000000000003</v>
+        <v>0.7225000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>3.763</v>
+        <v>3.7633</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.04</v>
+        <v>-3.0408</v>
       </c>
       <c r="J7" t="n">
-        <v>4.446400000000001</v>
+        <v>4.4485</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9706</v>
+        <v>3.9726</v>
       </c>
       <c r="L7" t="n">
         <v>0.4758</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.7232</v>
+        <v>-3.726</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2074</v>
+        <v>-0.2094</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.5159</v>
+        <v>-3.5166</v>
       </c>
       <c r="P7" t="n">
         <v>-0.4679</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.5091</v>
+        <v>-3.5094</v>
       </c>
       <c r="R7" t="n">
-        <v>3.0412</v>
+        <v>3.0415</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4118</v>
+        <v>0.4122</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7517999999999999</v>
+        <v>-0.7555000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1636</v>
+        <v>1.1677</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.6605</v>
+        <v>-2.6604</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2628</v>
+        <v>2.2626</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.9233</v>
+        <v>-4.9229</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1021,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8043</v>
+        <v>-3.805</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4442</v>
+        <v>-1.446</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3601</v>
+        <v>-2.3589</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5881</v>
+        <v>-2.5872</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3964</v>
+        <v>-0.3977999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1919</v>
+        <v>-2.1894</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4273999999999999</v>
+        <v>0.4307000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9705</v>
+        <v>0.9707</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.543</v>
+        <v>-0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.0155</v>
+        <v>-3.0179</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3669</v>
+        <v>-1.3684</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6487</v>
+        <v>-1.6494</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4037</v>
+        <v>1.4038</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8715</v>
+        <v>-1.8717</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2752</v>
+        <v>3.2755</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.599</v>
+        <v>-0.6007</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1987</v>
+        <v>-1.2035</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5997</v>
+        <v>0.6027</v>
       </c>
       <c r="V8" t="n">
         <v>-2.0209</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1986</v>
+        <v>1.1985</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.2195</v>
+        <v>-3.2194</v>
       </c>
     </row>
     <row r="9">
@@ -1111,34 +1099,34 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8243</v>
+        <v>-3.8246</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3184</v>
+        <v>-3.319</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5059</v>
+        <v>-0.5056</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0549</v>
+        <v>-2.0546</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1579</v>
+        <v>-1.1576</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8969</v>
+        <v>-0.897</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7863</v>
+        <v>-0.7859</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8229</v>
+        <v>-0.8225</v>
       </c>
       <c r="L9" t="n">
         <v>0.0366</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2686</v>
+        <v>-1.2688</v>
       </c>
       <c r="N9" t="n">
         <v>-0.3351</v>
@@ -1147,28 +1135,28 @@
         <v>-0.9336</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.0413</v>
+        <v>-3.0416</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.5092</v>
+        <v>-3.5094</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4678</v>
+        <v>0.468</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2077</v>
+        <v>0.2074</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.08710000000000001</v>
+        <v>-0.08789999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2948</v>
+        <v>0.2953</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0642</v>
+        <v>1.0641</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0642</v>
+        <v>1.0641</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1177,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2796</v>
+        <v>-5.2768</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6647</v>
+        <v>-2.6633</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6149</v>
+        <v>-2.6135</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.8514</v>
+        <v>-6.847899999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9701</v>
+        <v>-1.9697</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.8813</v>
+        <v>-4.878299999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7561</v>
+        <v>-2.7497</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7692</v>
+        <v>-0.7672999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9868</v>
+        <v>-1.9824</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.0953</v>
+        <v>-4.0982</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2008</v>
+        <v>-1.2025</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.8944</v>
+        <v>-2.8957</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1055</v>
+        <v>2.1056</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.6376</v>
+        <v>-1.6377</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7431</v>
+        <v>3.7434</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8893</v>
+        <v>-1.8901</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.9957</v>
+        <v>-2.0004</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1064</v>
+        <v>0.1104</v>
       </c>
       <c r="V10" t="n">
         <v>1.3555</v>
       </c>
       <c r="W10" t="n">
-        <v>3.7247</v>
+        <v>3.7245</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3692</v>
+        <v>-2.369</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1255,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5416</v>
+        <v>-6.5419</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.928</v>
+        <v>-1.9292</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.6137</v>
+        <v>-4.6127</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8747</v>
+        <v>-3.8741</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5686</v>
+        <v>-1.5681</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3061</v>
+        <v>-2.306</v>
       </c>
       <c r="J11" t="n">
-        <v>0.006500000000000061</v>
+        <v>0.007900000000000018</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8912</v>
+        <v>-0.8899999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8975</v>
+        <v>0.8978999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.8812</v>
+        <v>-3.882</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6775</v>
+        <v>-0.6780999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.2037</v>
+        <v>-3.2039</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1055</v>
+        <v>-2.1057</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.5092</v>
+        <v>-3.5094</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4036</v>
+        <v>1.4038</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6958</v>
+        <v>-0.6965</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6880999999999999</v>
+        <v>-0.6904</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.007699999999999999</v>
+        <v>-0.006100000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1344000000000001</v>
+        <v>0.1343999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2628</v>
+        <v>2.2626</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1284</v>
+        <v>-2.1283</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1333,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.630800000000001</v>
+        <v>-6.6328</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6966</v>
+        <v>-4.7006</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9342</v>
+        <v>-1.9323</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.2741</v>
+        <v>-5.274100000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.6497</v>
+        <v>-4.6486</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6244000000000001</v>
+        <v>-0.6255000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8557</v>
+        <v>-1.8531</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.9538</v>
+        <v>-2.9512</v>
       </c>
       <c r="L12" t="n">
         <v>1.0981</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.4186</v>
+        <v>-3.421</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6959</v>
+        <v>-1.6975</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7225</v>
+        <v>-1.7236</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8716</v>
+        <v>1.8718</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0413</v>
+        <v>-3.0415</v>
       </c>
       <c r="R12" t="n">
-        <v>4.9129</v>
+        <v>4.9132</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5408000000000001</v>
+        <v>-0.5432</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8639</v>
+        <v>-0.8702</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3229</v>
+        <v>0.3268</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.6874</v>
+        <v>-2.6872</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0642</v>
+        <v>1.0641</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.7516</v>
+        <v>-3.7514</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1411,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.5911</v>
+        <v>-11.5901</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.8863</v>
+        <v>-8.886000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7048</v>
+        <v>-2.7041</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.4909</v>
+        <v>-9.488399999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1919</v>
+        <v>-2.1917</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.298999999999999</v>
+        <v>-7.2969</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.2761</v>
+        <v>-5.2728</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1808</v>
+        <v>-1.18</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0953</v>
+        <v>-4.0928</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.2147</v>
+        <v>-4.2157</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0111</v>
+        <v>-1.0117</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.2038</v>
+        <v>-3.204</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.4037</v>
+        <v>-1.4038</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.5092</v>
+        <v>-3.5094</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1055</v>
+        <v>2.1057</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2331</v>
+        <v>0.232</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2355</v>
+        <v>-0.238</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4686</v>
+        <v>0.47</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9298000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1344</v>
+        <v>0.1343</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1489,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.3545</v>
+        <v>-15.3498</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.429</v>
+        <v>-14.4261</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9255</v>
+        <v>-0.9236000000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>-11.7365</v>
+        <v>-11.7297</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.29</v>
+        <v>-3.2883</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.446400000000001</v>
+        <v>-8.4415</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.157100000000001</v>
+        <v>-6.148099999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.4279</v>
+        <v>-1.4248</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.7291</v>
+        <v>-4.7233</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.5793</v>
+        <v>-5.5816</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.862</v>
+        <v>-1.8635</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7173</v>
+        <v>-3.7182</v>
       </c>
       <c r="P14" t="n">
         <v>-1.1698</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.4863</v>
+        <v>-7.4868</v>
       </c>
       <c r="R14" t="n">
-        <v>6.3166</v>
+        <v>6.317</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0785</v>
+        <v>-2.0804</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.1239</v>
+        <v>-2.1293</v>
       </c>
       <c r="U14" t="n">
-        <v>0.04549999999999998</v>
+        <v>0.04900000000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3696999999999999</v>
+        <v>-0.3697999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3385</v>
+        <v>1.3381</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7082</v>
+        <v>-1.7079</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1567,67 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-47.7125</v>
+        <v>-47.7109</v>
       </c>
       <c r="E15" t="n">
-        <v>-28.779</v>
+        <v>-28.7945</v>
       </c>
       <c r="F15" t="n">
-        <v>-18.9335</v>
+        <v>-18.916</v>
       </c>
       <c r="G15" t="n">
-        <v>-39.623</v>
+        <v>-39.6091</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.177199999999999</v>
+        <v>-9.1785</v>
       </c>
       <c r="I15" t="n">
-        <v>-30.4461</v>
+        <v>-30.4308</v>
       </c>
       <c r="J15" t="n">
-        <v>2.428900000000001</v>
+        <v>2.469600000000002</v>
       </c>
       <c r="K15" t="n">
-        <v>2.015500000000001</v>
+        <v>2.0312</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4139000000000008</v>
+        <v>0.4382000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-42.0519</v>
+        <v>-42.0789</v>
       </c>
       <c r="N15" t="n">
-        <v>-11.1924</v>
+        <v>-11.2099</v>
       </c>
       <c r="O15" t="n">
-        <v>-30.86</v>
+        <v>-30.8689</v>
       </c>
       <c r="P15" t="n">
-        <v>4.678799999999999</v>
+        <v>4.679199999999998</v>
       </c>
       <c r="Q15" t="n">
-        <v>-37.4312</v>
+        <v>-37.4339</v>
       </c>
       <c r="R15" t="n">
-        <v>42.1101</v>
+        <v>42.1134</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.8566</v>
+        <v>-5.8694</v>
       </c>
       <c r="T15" t="n">
-        <v>-12.4223</v>
+        <v>-12.474</v>
       </c>
       <c r="U15" t="n">
-        <v>6.5654</v>
+        <v>6.6047</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.911900000000001</v>
+        <v>-6.9117</v>
       </c>
       <c r="W15" t="n">
-        <v>18.6455</v>
+        <v>18.6434</v>
       </c>
       <c r="X15" t="n">
-        <v>-25.5574</v>
+        <v>-25.5553</v>
       </c>
     </row>
   </sheetData>
